--- a/T6_PopularGraphs/Boston_dataset.xlsx
+++ b/T6_PopularGraphs/Boston_dataset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alanvazquez/Documents/GitHub/TEC-IN2039/Session_3_Categorical_Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alanvazquez/Documents/GitHub/TEC-IN2039-EN/T6_PopularGraphs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D9F525-3111-6A40-9F28-03090E7F911C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6AC3A6-7F56-774D-864C-ABEA54198619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31240" yWindow="1660" windowWidth="27640" windowHeight="16440" xr2:uid="{3281DF35-1E64-4246-B8ED-E974308B8BBB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>crim</t>
   </si>
@@ -81,15 +81,6 @@
   </si>
   <si>
     <t>medv</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>High</t>
   </si>
 </sst>
 </file>
@@ -154,9 +145,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -194,7 +185,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -300,7 +291,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -442,7 +433,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -522,8 +513,8 @@
       <c r="H2">
         <v>4.09</v>
       </c>
-      <c r="I2" t="s">
-        <v>14</v>
+      <c r="I2">
+        <v>0</v>
       </c>
       <c r="J2">
         <v>296</v>
@@ -566,8 +557,8 @@
       <c r="H3">
         <v>4.9671000000000003</v>
       </c>
-      <c r="I3" t="s">
-        <v>14</v>
+      <c r="I3">
+        <v>0</v>
       </c>
       <c r="J3">
         <v>242</v>
@@ -610,8 +601,8 @@
       <c r="H4">
         <v>4.9671000000000003</v>
       </c>
-      <c r="I4" t="s">
-        <v>14</v>
+      <c r="I4">
+        <v>0</v>
       </c>
       <c r="J4">
         <v>242</v>
@@ -654,8 +645,8 @@
       <c r="H5">
         <v>6.0621999999999998</v>
       </c>
-      <c r="I5" t="s">
-        <v>14</v>
+      <c r="I5">
+        <v>0</v>
       </c>
       <c r="J5">
         <v>222</v>
@@ -698,8 +689,8 @@
       <c r="H6">
         <v>6.0621999999999998</v>
       </c>
-      <c r="I6" t="s">
-        <v>14</v>
+      <c r="I6">
+        <v>0</v>
       </c>
       <c r="J6">
         <v>222</v>
@@ -742,8 +733,8 @@
       <c r="H7">
         <v>6.0621999999999998</v>
       </c>
-      <c r="I7" t="s">
-        <v>14</v>
+      <c r="I7">
+        <v>0</v>
       </c>
       <c r="J7">
         <v>222</v>
@@ -786,8 +777,8 @@
       <c r="H8">
         <v>5.5605000000000002</v>
       </c>
-      <c r="I8" t="s">
-        <v>15</v>
+      <c r="I8">
+        <v>1</v>
       </c>
       <c r="J8">
         <v>311</v>
@@ -830,8 +821,8 @@
       <c r="H9">
         <v>5.9504999999999999</v>
       </c>
-      <c r="I9" t="s">
-        <v>15</v>
+      <c r="I9">
+        <v>1</v>
       </c>
       <c r="J9">
         <v>311</v>
@@ -874,8 +865,8 @@
       <c r="H10">
         <v>6.0820999999999996</v>
       </c>
-      <c r="I10" t="s">
-        <v>15</v>
+      <c r="I10">
+        <v>1</v>
       </c>
       <c r="J10">
         <v>311</v>
@@ -918,8 +909,8 @@
       <c r="H11">
         <v>6.5921000000000003</v>
       </c>
-      <c r="I11" t="s">
-        <v>15</v>
+      <c r="I11">
+        <v>1</v>
       </c>
       <c r="J11">
         <v>311</v>
@@ -962,8 +953,8 @@
       <c r="H12">
         <v>6.3467000000000002</v>
       </c>
-      <c r="I12" t="s">
-        <v>15</v>
+      <c r="I12">
+        <v>1</v>
       </c>
       <c r="J12">
         <v>311</v>
@@ -1006,8 +997,8 @@
       <c r="H13">
         <v>6.2267000000000001</v>
       </c>
-      <c r="I13" t="s">
-        <v>15</v>
+      <c r="I13">
+        <v>1</v>
       </c>
       <c r="J13">
         <v>311</v>
@@ -1050,8 +1041,8 @@
       <c r="H14">
         <v>5.4508999999999999</v>
       </c>
-      <c r="I14" t="s">
-        <v>15</v>
+      <c r="I14">
+        <v>1</v>
       </c>
       <c r="J14">
         <v>311</v>
@@ -1094,8 +1085,8 @@
       <c r="H15">
         <v>4.7074999999999996</v>
       </c>
-      <c r="I15" t="s">
-        <v>15</v>
+      <c r="I15">
+        <v>1</v>
       </c>
       <c r="J15">
         <v>307</v>
@@ -1138,8 +1129,8 @@
       <c r="H16">
         <v>4.4619</v>
       </c>
-      <c r="I16" t="s">
-        <v>15</v>
+      <c r="I16">
+        <v>1</v>
       </c>
       <c r="J16">
         <v>307</v>
@@ -1182,8 +1173,8 @@
       <c r="H17">
         <v>4.4985999999999997</v>
       </c>
-      <c r="I17" t="s">
-        <v>15</v>
+      <c r="I17">
+        <v>1</v>
       </c>
       <c r="J17">
         <v>307</v>
@@ -1226,8 +1217,8 @@
       <c r="H18">
         <v>4.4985999999999997</v>
       </c>
-      <c r="I18" t="s">
-        <v>15</v>
+      <c r="I18">
+        <v>1</v>
       </c>
       <c r="J18">
         <v>307</v>
@@ -1270,8 +1261,8 @@
       <c r="H19">
         <v>4.2579000000000002</v>
       </c>
-      <c r="I19" t="s">
-        <v>15</v>
+      <c r="I19">
+        <v>1</v>
       </c>
       <c r="J19">
         <v>307</v>
@@ -1314,8 +1305,8 @@
       <c r="H20">
         <v>3.7965</v>
       </c>
-      <c r="I20" t="s">
-        <v>15</v>
+      <c r="I20">
+        <v>1</v>
       </c>
       <c r="J20">
         <v>307</v>
@@ -1358,8 +1349,8 @@
       <c r="H21">
         <v>3.7965</v>
       </c>
-      <c r="I21" t="s">
-        <v>15</v>
+      <c r="I21">
+        <v>1</v>
       </c>
       <c r="J21">
         <v>307</v>
@@ -1402,8 +1393,8 @@
       <c r="H22">
         <v>3.7978999999999998</v>
       </c>
-      <c r="I22" t="s">
-        <v>15</v>
+      <c r="I22">
+        <v>1</v>
       </c>
       <c r="J22">
         <v>307</v>
@@ -1446,8 +1437,8 @@
       <c r="H23">
         <v>4.0122999999999998</v>
       </c>
-      <c r="I23" t="s">
-        <v>15</v>
+      <c r="I23">
+        <v>1</v>
       </c>
       <c r="J23">
         <v>307</v>
@@ -1490,8 +1481,8 @@
       <c r="H24">
         <v>3.9769000000000001</v>
       </c>
-      <c r="I24" t="s">
-        <v>15</v>
+      <c r="I24">
+        <v>1</v>
       </c>
       <c r="J24">
         <v>307</v>
@@ -1534,8 +1525,8 @@
       <c r="H25">
         <v>4.0952000000000002</v>
       </c>
-      <c r="I25" t="s">
-        <v>15</v>
+      <c r="I25">
+        <v>1</v>
       </c>
       <c r="J25">
         <v>307</v>
@@ -1578,8 +1569,8 @@
       <c r="H26">
         <v>4.3996000000000004</v>
       </c>
-      <c r="I26" t="s">
-        <v>15</v>
+      <c r="I26">
+        <v>1</v>
       </c>
       <c r="J26">
         <v>307</v>
@@ -1622,8 +1613,8 @@
       <c r="H27">
         <v>4.4546000000000001</v>
       </c>
-      <c r="I27" t="s">
-        <v>15</v>
+      <c r="I27">
+        <v>1</v>
       </c>
       <c r="J27">
         <v>307</v>
@@ -1666,8 +1657,8 @@
       <c r="H28">
         <v>4.6820000000000004</v>
       </c>
-      <c r="I28" t="s">
-        <v>15</v>
+      <c r="I28">
+        <v>1</v>
       </c>
       <c r="J28">
         <v>307</v>
@@ -1710,8 +1701,8 @@
       <c r="H29">
         <v>4.4534000000000002</v>
       </c>
-      <c r="I29" t="s">
-        <v>15</v>
+      <c r="I29">
+        <v>1</v>
       </c>
       <c r="J29">
         <v>307</v>
@@ -1754,8 +1745,8 @@
       <c r="H30">
         <v>4.4546999999999999</v>
       </c>
-      <c r="I30" t="s">
-        <v>15</v>
+      <c r="I30">
+        <v>1</v>
       </c>
       <c r="J30">
         <v>307</v>
@@ -1798,8 +1789,8 @@
       <c r="H31">
         <v>4.2389999999999999</v>
       </c>
-      <c r="I31" t="s">
-        <v>15</v>
+      <c r="I31">
+        <v>1</v>
       </c>
       <c r="J31">
         <v>307</v>
@@ -1842,8 +1833,8 @@
       <c r="H32">
         <v>4.2329999999999997</v>
       </c>
-      <c r="I32" t="s">
-        <v>15</v>
+      <c r="I32">
+        <v>1</v>
       </c>
       <c r="J32">
         <v>307</v>
@@ -1886,8 +1877,8 @@
       <c r="H33">
         <v>4.1749999999999998</v>
       </c>
-      <c r="I33" t="s">
-        <v>15</v>
+      <c r="I33">
+        <v>1</v>
       </c>
       <c r="J33">
         <v>307</v>
@@ -1930,8 +1921,8 @@
       <c r="H34">
         <v>3.99</v>
       </c>
-      <c r="I34" t="s">
-        <v>15</v>
+      <c r="I34">
+        <v>1</v>
       </c>
       <c r="J34">
         <v>307</v>
@@ -1974,8 +1965,8 @@
       <c r="H35">
         <v>3.7871999999999999</v>
       </c>
-      <c r="I35" t="s">
-        <v>15</v>
+      <c r="I35">
+        <v>1</v>
       </c>
       <c r="J35">
         <v>307</v>
@@ -2018,8 +2009,8 @@
       <c r="H36">
         <v>3.7597999999999998</v>
       </c>
-      <c r="I36" t="s">
-        <v>15</v>
+      <c r="I36">
+        <v>1</v>
       </c>
       <c r="J36">
         <v>307</v>
@@ -2062,8 +2053,8 @@
       <c r="H37">
         <v>3.3603000000000001</v>
       </c>
-      <c r="I37" t="s">
-        <v>15</v>
+      <c r="I37">
+        <v>1</v>
       </c>
       <c r="J37">
         <v>279</v>
@@ -2106,8 +2097,8 @@
       <c r="H38">
         <v>3.3778999999999999</v>
       </c>
-      <c r="I38" t="s">
-        <v>15</v>
+      <c r="I38">
+        <v>1</v>
       </c>
       <c r="J38">
         <v>279</v>
@@ -2150,8 +2141,8 @@
       <c r="H39">
         <v>3.9342000000000001</v>
       </c>
-      <c r="I39" t="s">
-        <v>15</v>
+      <c r="I39">
+        <v>1</v>
       </c>
       <c r="J39">
         <v>279</v>
@@ -2194,8 +2185,8 @@
       <c r="H40">
         <v>3.8473000000000002</v>
       </c>
-      <c r="I40" t="s">
-        <v>15</v>
+      <c r="I40">
+        <v>1</v>
       </c>
       <c r="J40">
         <v>279</v>
@@ -2238,8 +2229,8 @@
       <c r="H41">
         <v>5.4010999999999996</v>
       </c>
-      <c r="I41" t="s">
-        <v>14</v>
+      <c r="I41">
+        <v>0</v>
       </c>
       <c r="J41">
         <v>252</v>
@@ -2282,8 +2273,8 @@
       <c r="H42">
         <v>5.4010999999999996</v>
       </c>
-      <c r="I42" t="s">
-        <v>14</v>
+      <c r="I42">
+        <v>0</v>
       </c>
       <c r="J42">
         <v>252</v>
@@ -2326,8 +2317,8 @@
       <c r="H43">
         <v>5.7209000000000003</v>
       </c>
-      <c r="I43" t="s">
-        <v>14</v>
+      <c r="I43">
+        <v>0</v>
       </c>
       <c r="J43">
         <v>233</v>
@@ -2370,8 +2361,8 @@
       <c r="H44">
         <v>5.7209000000000003</v>
       </c>
-      <c r="I44" t="s">
-        <v>14</v>
+      <c r="I44">
+        <v>0</v>
       </c>
       <c r="J44">
         <v>233</v>
@@ -2414,8 +2405,8 @@
       <c r="H45">
         <v>5.7209000000000003</v>
       </c>
-      <c r="I45" t="s">
-        <v>14</v>
+      <c r="I45">
+        <v>0</v>
       </c>
       <c r="J45">
         <v>233</v>
@@ -2458,8 +2449,8 @@
       <c r="H46">
         <v>5.7209000000000003</v>
       </c>
-      <c r="I46" t="s">
-        <v>14</v>
+      <c r="I46">
+        <v>0</v>
       </c>
       <c r="J46">
         <v>233</v>
@@ -2502,8 +2493,8 @@
       <c r="H47">
         <v>5.1003999999999996</v>
       </c>
-      <c r="I47" t="s">
-        <v>14</v>
+      <c r="I47">
+        <v>0</v>
       </c>
       <c r="J47">
         <v>233</v>
@@ -2546,8 +2537,8 @@
       <c r="H48">
         <v>5.1003999999999996</v>
       </c>
-      <c r="I48" t="s">
-        <v>14</v>
+      <c r="I48">
+        <v>0</v>
       </c>
       <c r="J48">
         <v>233</v>
@@ -2590,8 +2581,8 @@
       <c r="H49">
         <v>5.6894</v>
       </c>
-      <c r="I49" t="s">
-        <v>14</v>
+      <c r="I49">
+        <v>0</v>
       </c>
       <c r="J49">
         <v>233</v>
@@ -2634,8 +2625,8 @@
       <c r="H50">
         <v>5.87</v>
       </c>
-      <c r="I50" t="s">
-        <v>14</v>
+      <c r="I50">
+        <v>0</v>
       </c>
       <c r="J50">
         <v>233</v>
@@ -2678,8 +2669,8 @@
       <c r="H51">
         <v>6.0876999999999999</v>
       </c>
-      <c r="I51" t="s">
-        <v>14</v>
+      <c r="I51">
+        <v>0</v>
       </c>
       <c r="J51">
         <v>233</v>
@@ -2722,8 +2713,8 @@
       <c r="H52">
         <v>6.8147000000000002</v>
       </c>
-      <c r="I52" t="s">
-        <v>15</v>
+      <c r="I52">
+        <v>1</v>
       </c>
       <c r="J52">
         <v>243</v>
@@ -2766,8 +2757,8 @@
       <c r="H53">
         <v>6.8147000000000002</v>
       </c>
-      <c r="I53" t="s">
-        <v>15</v>
+      <c r="I53">
+        <v>1</v>
       </c>
       <c r="J53">
         <v>243</v>
@@ -2810,8 +2801,8 @@
       <c r="H54">
         <v>6.8147000000000002</v>
       </c>
-      <c r="I54" t="s">
-        <v>15</v>
+      <c r="I54">
+        <v>1</v>
       </c>
       <c r="J54">
         <v>243</v>
@@ -2854,8 +2845,8 @@
       <c r="H55">
         <v>6.8147000000000002</v>
       </c>
-      <c r="I55" t="s">
-        <v>15</v>
+      <c r="I55">
+        <v>1</v>
       </c>
       <c r="J55">
         <v>243</v>
@@ -2898,8 +2889,8 @@
       <c r="H56">
         <v>7.3197000000000001</v>
       </c>
-      <c r="I56" t="s">
-        <v>14</v>
+      <c r="I56">
+        <v>0</v>
       </c>
       <c r="J56">
         <v>469</v>
@@ -2942,8 +2933,8 @@
       <c r="H57">
         <v>8.6966000000000001</v>
       </c>
-      <c r="I57" t="s">
-        <v>15</v>
+      <c r="I57">
+        <v>1</v>
       </c>
       <c r="J57">
         <v>226</v>
@@ -2986,8 +2977,8 @@
       <c r="H58">
         <v>9.1875999999999998</v>
       </c>
-      <c r="I58" t="s">
-        <v>14</v>
+      <c r="I58">
+        <v>0</v>
       </c>
       <c r="J58">
         <v>313</v>
@@ -3030,8 +3021,8 @@
       <c r="H59">
         <v>8.3247999999999998</v>
       </c>
-      <c r="I59" t="s">
-        <v>15</v>
+      <c r="I59">
+        <v>1</v>
       </c>
       <c r="J59">
         <v>256</v>
@@ -3074,8 +3065,8 @@
       <c r="H60">
         <v>7.8148</v>
       </c>
-      <c r="I60" t="s">
-        <v>16</v>
+      <c r="I60">
+        <v>2</v>
       </c>
       <c r="J60">
         <v>284</v>
@@ -3118,8 +3109,8 @@
       <c r="H61">
         <v>6.9320000000000004</v>
       </c>
-      <c r="I61" t="s">
-        <v>16</v>
+      <c r="I61">
+        <v>2</v>
       </c>
       <c r="J61">
         <v>284</v>
@@ -3162,8 +3153,8 @@
       <c r="H62">
         <v>7.2253999999999996</v>
       </c>
-      <c r="I62" t="s">
-        <v>16</v>
+      <c r="I62">
+        <v>2</v>
       </c>
       <c r="J62">
         <v>284</v>
@@ -3206,8 +3197,8 @@
       <c r="H63">
         <v>6.8185000000000002</v>
       </c>
-      <c r="I63" t="s">
-        <v>16</v>
+      <c r="I63">
+        <v>2</v>
       </c>
       <c r="J63">
         <v>284</v>
@@ -3250,8 +3241,8 @@
       <c r="H64">
         <v>7.2255000000000003</v>
       </c>
-      <c r="I64" t="s">
-        <v>16</v>
+      <c r="I64">
+        <v>2</v>
       </c>
       <c r="J64">
         <v>284</v>
@@ -3294,8 +3285,8 @@
       <c r="H65">
         <v>7.9809000000000001</v>
       </c>
-      <c r="I65" t="s">
-        <v>16</v>
+      <c r="I65">
+        <v>2</v>
       </c>
       <c r="J65">
         <v>284</v>
@@ -3338,8 +3329,8 @@
       <c r="H66">
         <v>9.2228999999999992</v>
       </c>
-      <c r="I66" t="s">
-        <v>14</v>
+      <c r="I66">
+        <v>0</v>
       </c>
       <c r="J66">
         <v>216</v>
@@ -3382,8 +3373,8 @@
       <c r="H67">
         <v>6.6115000000000004</v>
       </c>
-      <c r="I67" t="s">
-        <v>15</v>
+      <c r="I67">
+        <v>1</v>
       </c>
       <c r="J67">
         <v>337</v>
@@ -3426,8 +3417,8 @@
       <c r="H68">
         <v>6.6115000000000004</v>
       </c>
-      <c r="I68" t="s">
-        <v>15</v>
+      <c r="I68">
+        <v>1</v>
       </c>
       <c r="J68">
         <v>337</v>
@@ -3470,8 +3461,8 @@
       <c r="H69">
         <v>6.4980000000000002</v>
       </c>
-      <c r="I69" t="s">
-        <v>15</v>
+      <c r="I69">
+        <v>1</v>
       </c>
       <c r="J69">
         <v>345</v>
@@ -3514,8 +3505,8 @@
       <c r="H70">
         <v>6.4980000000000002</v>
       </c>
-      <c r="I70" t="s">
-        <v>15</v>
+      <c r="I70">
+        <v>1</v>
       </c>
       <c r="J70">
         <v>345</v>
@@ -3558,8 +3549,8 @@
       <c r="H71">
         <v>6.4980000000000002</v>
       </c>
-      <c r="I71" t="s">
-        <v>15</v>
+      <c r="I71">
+        <v>1</v>
       </c>
       <c r="J71">
         <v>345</v>
@@ -3602,8 +3593,8 @@
       <c r="H72">
         <v>5.2873000000000001</v>
       </c>
-      <c r="I72" t="s">
-        <v>15</v>
+      <c r="I72">
+        <v>1</v>
       </c>
       <c r="J72">
         <v>305</v>
@@ -3646,8 +3637,8 @@
       <c r="H73">
         <v>5.2873000000000001</v>
       </c>
-      <c r="I73" t="s">
-        <v>15</v>
+      <c r="I73">
+        <v>1</v>
       </c>
       <c r="J73">
         <v>305</v>
@@ -3690,8 +3681,8 @@
       <c r="H74">
         <v>5.2873000000000001</v>
       </c>
-      <c r="I74" t="s">
-        <v>15</v>
+      <c r="I74">
+        <v>1</v>
       </c>
       <c r="J74">
         <v>305</v>
@@ -3734,8 +3725,8 @@
       <c r="H75">
         <v>5.2873000000000001</v>
       </c>
-      <c r="I75" t="s">
-        <v>15</v>
+      <c r="I75">
+        <v>1</v>
       </c>
       <c r="J75">
         <v>305</v>
@@ -3778,8 +3769,8 @@
       <c r="H76">
         <v>4.2515000000000001</v>
       </c>
-      <c r="I76" t="s">
-        <v>15</v>
+      <c r="I76">
+        <v>1</v>
       </c>
       <c r="J76">
         <v>398</v>
@@ -3822,8 +3813,8 @@
       <c r="H77">
         <v>4.5026000000000002</v>
       </c>
-      <c r="I77" t="s">
-        <v>15</v>
+      <c r="I77">
+        <v>1</v>
       </c>
       <c r="J77">
         <v>398</v>
@@ -3866,8 +3857,8 @@
       <c r="H78">
         <v>4.0522</v>
       </c>
-      <c r="I78" t="s">
-        <v>15</v>
+      <c r="I78">
+        <v>1</v>
       </c>
       <c r="J78">
         <v>398</v>
@@ -3910,8 +3901,8 @@
       <c r="H79">
         <v>4.0904999999999996</v>
       </c>
-      <c r="I79" t="s">
-        <v>15</v>
+      <c r="I79">
+        <v>1</v>
       </c>
       <c r="J79">
         <v>398</v>
@@ -3954,8 +3945,8 @@
       <c r="H80">
         <v>5.0141</v>
       </c>
-      <c r="I80" t="s">
-        <v>15</v>
+      <c r="I80">
+        <v>1</v>
       </c>
       <c r="J80">
         <v>398</v>
@@ -3998,8 +3989,8 @@
       <c r="H81">
         <v>4.5026000000000002</v>
       </c>
-      <c r="I81" t="s">
-        <v>15</v>
+      <c r="I81">
+        <v>1</v>
       </c>
       <c r="J81">
         <v>398</v>
@@ -4042,8 +4033,8 @@
       <c r="H82">
         <v>5.4006999999999996</v>
       </c>
-      <c r="I82" t="s">
-        <v>15</v>
+      <c r="I82">
+        <v>1</v>
       </c>
       <c r="J82">
         <v>281</v>
@@ -4086,8 +4077,8 @@
       <c r="H83">
         <v>5.4006999999999996</v>
       </c>
-      <c r="I83" t="s">
-        <v>15</v>
+      <c r="I83">
+        <v>1</v>
       </c>
       <c r="J83">
         <v>281</v>
@@ -4130,8 +4121,8 @@
       <c r="H84">
         <v>5.4006999999999996</v>
       </c>
-      <c r="I84" t="s">
-        <v>15</v>
+      <c r="I84">
+        <v>1</v>
       </c>
       <c r="J84">
         <v>281</v>
@@ -4174,8 +4165,8 @@
       <c r="H85">
         <v>5.4006999999999996</v>
       </c>
-      <c r="I85" t="s">
-        <v>15</v>
+      <c r="I85">
+        <v>1</v>
       </c>
       <c r="J85">
         <v>281</v>
@@ -4218,8 +4209,8 @@
       <c r="H86">
         <v>4.7793999999999999</v>
       </c>
-      <c r="I86" t="s">
-        <v>14</v>
+      <c r="I86">
+        <v>0</v>
       </c>
       <c r="J86">
         <v>247</v>
@@ -4262,8 +4253,8 @@
       <c r="H87">
         <v>4.4377000000000004</v>
       </c>
-      <c r="I87" t="s">
-        <v>14</v>
+      <c r="I87">
+        <v>0</v>
       </c>
       <c r="J87">
         <v>247</v>
@@ -4306,8 +4297,8 @@
       <c r="H88">
         <v>4.4272</v>
       </c>
-      <c r="I88" t="s">
-        <v>14</v>
+      <c r="I88">
+        <v>0</v>
       </c>
       <c r="J88">
         <v>247</v>
@@ -4350,8 +4341,8 @@
       <c r="H89">
         <v>3.7475999999999998</v>
       </c>
-      <c r="I89" t="s">
-        <v>14</v>
+      <c r="I89">
+        <v>0</v>
       </c>
       <c r="J89">
         <v>247</v>
@@ -4394,8 +4385,8 @@
       <c r="H90">
         <v>3.4217</v>
       </c>
-      <c r="I90" t="s">
-        <v>14</v>
+      <c r="I90">
+        <v>0</v>
       </c>
       <c r="J90">
         <v>270</v>
@@ -4438,8 +4429,8 @@
       <c r="H91">
         <v>3.4144999999999999</v>
       </c>
-      <c r="I91" t="s">
-        <v>14</v>
+      <c r="I91">
+        <v>0</v>
       </c>
       <c r="J91">
         <v>270</v>
@@ -4482,8 +4473,8 @@
       <c r="H92">
         <v>3.0922999999999998</v>
       </c>
-      <c r="I92" t="s">
-        <v>14</v>
+      <c r="I92">
+        <v>0</v>
       </c>
       <c r="J92">
         <v>270</v>
@@ -4526,8 +4517,8 @@
       <c r="H93">
         <v>3.0920999999999998</v>
       </c>
-      <c r="I93" t="s">
-        <v>14</v>
+      <c r="I93">
+        <v>0</v>
       </c>
       <c r="J93">
         <v>270</v>
@@ -4570,8 +4561,8 @@
       <c r="H94">
         <v>3.6659000000000002</v>
       </c>
-      <c r="I94" t="s">
-        <v>15</v>
+      <c r="I94">
+        <v>1</v>
       </c>
       <c r="J94">
         <v>270</v>
@@ -4614,8 +4605,8 @@
       <c r="H95">
         <v>3.6659000000000002</v>
       </c>
-      <c r="I95" t="s">
-        <v>15</v>
+      <c r="I95">
+        <v>1</v>
       </c>
       <c r="J95">
         <v>270</v>
@@ -4658,8 +4649,8 @@
       <c r="H96">
         <v>3.6150000000000002</v>
       </c>
-      <c r="I96" t="s">
-        <v>15</v>
+      <c r="I96">
+        <v>1</v>
       </c>
       <c r="J96">
         <v>270</v>
@@ -4702,8 +4693,8 @@
       <c r="H97">
         <v>3.4952000000000001</v>
       </c>
-      <c r="I97" t="s">
-        <v>14</v>
+      <c r="I97">
+        <v>0</v>
       </c>
       <c r="J97">
         <v>276</v>
@@ -4746,8 +4737,8 @@
       <c r="H98">
         <v>3.4952000000000001</v>
       </c>
-      <c r="I98" t="s">
-        <v>14</v>
+      <c r="I98">
+        <v>0</v>
       </c>
       <c r="J98">
         <v>276</v>
@@ -4790,8 +4781,8 @@
       <c r="H99">
         <v>3.4952000000000001</v>
       </c>
-      <c r="I99" t="s">
-        <v>14</v>
+      <c r="I99">
+        <v>0</v>
       </c>
       <c r="J99">
         <v>276</v>
@@ -4834,8 +4825,8 @@
       <c r="H100">
         <v>3.4952000000000001</v>
       </c>
-      <c r="I100" t="s">
-        <v>14</v>
+      <c r="I100">
+        <v>0</v>
       </c>
       <c r="J100">
         <v>276</v>
@@ -4878,8 +4869,8 @@
       <c r="H101">
         <v>3.4952000000000001</v>
       </c>
-      <c r="I101" t="s">
-        <v>14</v>
+      <c r="I101">
+        <v>0</v>
       </c>
       <c r="J101">
         <v>276</v>
@@ -4922,8 +4913,8 @@
       <c r="H102">
         <v>2.7778</v>
       </c>
-      <c r="I102" t="s">
-        <v>15</v>
+      <c r="I102">
+        <v>1</v>
       </c>
       <c r="J102">
         <v>384</v>
@@ -4966,8 +4957,8 @@
       <c r="H103">
         <v>2.8561000000000001</v>
       </c>
-      <c r="I103" t="s">
-        <v>15</v>
+      <c r="I103">
+        <v>1</v>
       </c>
       <c r="J103">
         <v>384</v>
@@ -5010,8 +5001,8 @@
       <c r="H104">
         <v>2.7147000000000001</v>
       </c>
-      <c r="I104" t="s">
-        <v>15</v>
+      <c r="I104">
+        <v>1</v>
       </c>
       <c r="J104">
         <v>384</v>
@@ -5054,8 +5045,8 @@
       <c r="H105">
         <v>2.7147000000000001</v>
       </c>
-      <c r="I105" t="s">
-        <v>15</v>
+      <c r="I105">
+        <v>1</v>
       </c>
       <c r="J105">
         <v>384</v>
@@ -5098,8 +5089,8 @@
       <c r="H106">
         <v>2.4209999999999998</v>
       </c>
-      <c r="I106" t="s">
-        <v>15</v>
+      <c r="I106">
+        <v>1</v>
       </c>
       <c r="J106">
         <v>384</v>
@@ -5142,8 +5133,8 @@
       <c r="H107">
         <v>2.1069</v>
       </c>
-      <c r="I107" t="s">
-        <v>15</v>
+      <c r="I107">
+        <v>1</v>
       </c>
       <c r="J107">
         <v>384</v>
@@ -5186,8 +5177,8 @@
       <c r="H108">
         <v>2.2109999999999999</v>
       </c>
-      <c r="I108" t="s">
-        <v>15</v>
+      <c r="I108">
+        <v>1</v>
       </c>
       <c r="J108">
         <v>384</v>
@@ -5230,8 +5221,8 @@
       <c r="H109">
         <v>2.1223999999999998</v>
       </c>
-      <c r="I109" t="s">
-        <v>15</v>
+      <c r="I109">
+        <v>1</v>
       </c>
       <c r="J109">
         <v>384</v>
@@ -5274,8 +5265,8 @@
       <c r="H110">
         <v>2.4329000000000001</v>
       </c>
-      <c r="I110" t="s">
-        <v>15</v>
+      <c r="I110">
+        <v>1</v>
       </c>
       <c r="J110">
         <v>384</v>
@@ -5318,8 +5309,8 @@
       <c r="H111">
         <v>2.5451000000000001</v>
       </c>
-      <c r="I111" t="s">
-        <v>15</v>
+      <c r="I111">
+        <v>1</v>
       </c>
       <c r="J111">
         <v>384</v>
@@ -5362,8 +5353,8 @@
       <c r="H112">
         <v>2.7778</v>
       </c>
-      <c r="I112" t="s">
-        <v>15</v>
+      <c r="I112">
+        <v>1</v>
       </c>
       <c r="J112">
         <v>384</v>
@@ -5406,8 +5397,8 @@
       <c r="H113">
         <v>2.6775000000000002</v>
       </c>
-      <c r="I113" t="s">
-        <v>15</v>
+      <c r="I113">
+        <v>1</v>
       </c>
       <c r="J113">
         <v>432</v>
@@ -5450,8 +5441,8 @@
       <c r="H114">
         <v>2.3534000000000002</v>
       </c>
-      <c r="I114" t="s">
-        <v>15</v>
+      <c r="I114">
+        <v>1</v>
       </c>
       <c r="J114">
         <v>432</v>
@@ -5494,8 +5485,8 @@
       <c r="H115">
         <v>2.548</v>
       </c>
-      <c r="I115" t="s">
-        <v>15</v>
+      <c r="I115">
+        <v>1</v>
       </c>
       <c r="J115">
         <v>432</v>
@@ -5538,8 +5529,8 @@
       <c r="H116">
         <v>2.2565</v>
       </c>
-      <c r="I116" t="s">
-        <v>15</v>
+      <c r="I116">
+        <v>1</v>
       </c>
       <c r="J116">
         <v>432</v>
@@ -5582,8 +5573,8 @@
       <c r="H117">
         <v>2.4630999999999998</v>
       </c>
-      <c r="I117" t="s">
-        <v>15</v>
+      <c r="I117">
+        <v>1</v>
       </c>
       <c r="J117">
         <v>432</v>
@@ -5626,8 +5617,8 @@
       <c r="H118">
         <v>2.7301000000000002</v>
       </c>
-      <c r="I118" t="s">
-        <v>15</v>
+      <c r="I118">
+        <v>1</v>
       </c>
       <c r="J118">
         <v>432</v>
@@ -5670,8 +5661,8 @@
       <c r="H119">
         <v>2.7473999999999998</v>
       </c>
-      <c r="I119" t="s">
-        <v>15</v>
+      <c r="I119">
+        <v>1</v>
       </c>
       <c r="J119">
         <v>432</v>
@@ -5714,8 +5705,8 @@
       <c r="H120">
         <v>2.4775</v>
       </c>
-      <c r="I120" t="s">
-        <v>15</v>
+      <c r="I120">
+        <v>1</v>
       </c>
       <c r="J120">
         <v>432</v>
@@ -5758,8 +5749,8 @@
       <c r="H121">
         <v>2.7591999999999999</v>
       </c>
-      <c r="I121" t="s">
-        <v>15</v>
+      <c r="I121">
+        <v>1</v>
       </c>
       <c r="J121">
         <v>432</v>
@@ -5802,8 +5793,8 @@
       <c r="H122">
         <v>2.2576999999999998</v>
       </c>
-      <c r="I122" t="s">
-        <v>14</v>
+      <c r="I122">
+        <v>0</v>
       </c>
       <c r="J122">
         <v>188</v>
@@ -5846,8 +5837,8 @@
       <c r="H123">
         <v>2.1974</v>
       </c>
-      <c r="I123" t="s">
-        <v>14</v>
+      <c r="I123">
+        <v>0</v>
       </c>
       <c r="J123">
         <v>188</v>
@@ -5890,8 +5881,8 @@
       <c r="H124">
         <v>2.0869</v>
       </c>
-      <c r="I124" t="s">
-        <v>14</v>
+      <c r="I124">
+        <v>0</v>
       </c>
       <c r="J124">
         <v>188</v>
@@ -5934,8 +5925,8 @@
       <c r="H125">
         <v>1.9443999999999999</v>
       </c>
-      <c r="I125" t="s">
-        <v>14</v>
+      <c r="I125">
+        <v>0</v>
       </c>
       <c r="J125">
         <v>188</v>
@@ -5978,8 +5969,8 @@
       <c r="H126">
         <v>2.0063</v>
       </c>
-      <c r="I126" t="s">
-        <v>14</v>
+      <c r="I126">
+        <v>0</v>
       </c>
       <c r="J126">
         <v>188</v>
@@ -6022,8 +6013,8 @@
       <c r="H127">
         <v>1.9928999999999999</v>
       </c>
-      <c r="I127" t="s">
-        <v>14</v>
+      <c r="I127">
+        <v>0</v>
       </c>
       <c r="J127">
         <v>188</v>
@@ -6066,8 +6057,8 @@
       <c r="H128">
         <v>1.7572000000000001</v>
       </c>
-      <c r="I128" t="s">
-        <v>14</v>
+      <c r="I128">
+        <v>0</v>
       </c>
       <c r="J128">
         <v>188</v>
@@ -6110,8 +6101,8 @@
       <c r="H129">
         <v>1.7883</v>
       </c>
-      <c r="I129" t="s">
-        <v>15</v>
+      <c r="I129">
+        <v>1</v>
       </c>
       <c r="J129">
         <v>437</v>
@@ -6154,8 +6145,8 @@
       <c r="H130">
         <v>1.8125</v>
       </c>
-      <c r="I130" t="s">
-        <v>15</v>
+      <c r="I130">
+        <v>1</v>
       </c>
       <c r="J130">
         <v>437</v>
@@ -6198,8 +6189,8 @@
       <c r="H131">
         <v>1.9799</v>
       </c>
-      <c r="I131" t="s">
-        <v>15</v>
+      <c r="I131">
+        <v>1</v>
       </c>
       <c r="J131">
         <v>437</v>
@@ -6242,8 +6233,8 @@
       <c r="H132">
         <v>2.1185</v>
       </c>
-      <c r="I132" t="s">
-        <v>15</v>
+      <c r="I132">
+        <v>1</v>
       </c>
       <c r="J132">
         <v>437</v>
@@ -6286,8 +6277,8 @@
       <c r="H133">
         <v>2.2709999999999999</v>
       </c>
-      <c r="I133" t="s">
-        <v>15</v>
+      <c r="I133">
+        <v>1</v>
       </c>
       <c r="J133">
         <v>437</v>
@@ -6330,8 +6321,8 @@
       <c r="H134">
         <v>2.3273999999999999</v>
       </c>
-      <c r="I134" t="s">
-        <v>15</v>
+      <c r="I134">
+        <v>1</v>
       </c>
       <c r="J134">
         <v>437</v>
@@ -6374,8 +6365,8 @@
       <c r="H135">
         <v>2.4699</v>
       </c>
-      <c r="I135" t="s">
-        <v>15</v>
+      <c r="I135">
+        <v>1</v>
       </c>
       <c r="J135">
         <v>437</v>
@@ -6418,8 +6409,8 @@
       <c r="H136">
         <v>2.3460000000000001</v>
       </c>
-      <c r="I136" t="s">
-        <v>15</v>
+      <c r="I136">
+        <v>1</v>
       </c>
       <c r="J136">
         <v>437</v>
@@ -6462,8 +6453,8 @@
       <c r="H137">
         <v>2.1107</v>
       </c>
-      <c r="I137" t="s">
-        <v>15</v>
+      <c r="I137">
+        <v>1</v>
       </c>
       <c r="J137">
         <v>437</v>
@@ -6506,8 +6497,8 @@
       <c r="H138">
         <v>1.9669000000000001</v>
       </c>
-      <c r="I138" t="s">
-        <v>15</v>
+      <c r="I138">
+        <v>1</v>
       </c>
       <c r="J138">
         <v>437</v>
@@ -6550,8 +6541,8 @@
       <c r="H139">
         <v>1.8498000000000001</v>
       </c>
-      <c r="I139" t="s">
-        <v>15</v>
+      <c r="I139">
+        <v>1</v>
       </c>
       <c r="J139">
         <v>437</v>
@@ -6594,8 +6585,8 @@
       <c r="H140">
         <v>1.6686000000000001</v>
       </c>
-      <c r="I140" t="s">
-        <v>15</v>
+      <c r="I140">
+        <v>1</v>
       </c>
       <c r="J140">
         <v>437</v>
@@ -6638,8 +6629,8 @@
       <c r="H141">
         <v>1.6687000000000001</v>
       </c>
-      <c r="I141" t="s">
-        <v>15</v>
+      <c r="I141">
+        <v>1</v>
       </c>
       <c r="J141">
         <v>437</v>
@@ -6682,8 +6673,8 @@
       <c r="H142">
         <v>1.6119000000000001</v>
       </c>
-      <c r="I142" t="s">
-        <v>15</v>
+      <c r="I142">
+        <v>1</v>
       </c>
       <c r="J142">
         <v>437</v>
@@ -6726,8 +6717,8 @@
       <c r="H143">
         <v>1.4394</v>
       </c>
-      <c r="I143" t="s">
-        <v>15</v>
+      <c r="I143">
+        <v>1</v>
       </c>
       <c r="J143">
         <v>437</v>
@@ -6770,8 +6761,8 @@
       <c r="H144">
         <v>1.3216000000000001</v>
       </c>
-      <c r="I144" t="s">
-        <v>15</v>
+      <c r="I144">
+        <v>1</v>
       </c>
       <c r="J144">
         <v>403</v>
@@ -6814,8 +6805,8 @@
       <c r="H145">
         <v>1.4117999999999999</v>
       </c>
-      <c r="I145" t="s">
-        <v>15</v>
+      <c r="I145">
+        <v>1</v>
       </c>
       <c r="J145">
         <v>403</v>
@@ -6858,8 +6849,8 @@
       <c r="H146">
         <v>1.3459000000000001</v>
       </c>
-      <c r="I146" t="s">
-        <v>15</v>
+      <c r="I146">
+        <v>1</v>
       </c>
       <c r="J146">
         <v>403</v>
@@ -6902,8 +6893,8 @@
       <c r="H147">
         <v>1.4191</v>
       </c>
-      <c r="I147" t="s">
-        <v>15</v>
+      <c r="I147">
+        <v>1</v>
       </c>
       <c r="J147">
         <v>403</v>
@@ -6946,8 +6937,8 @@
       <c r="H148">
         <v>1.5165999999999999</v>
       </c>
-      <c r="I148" t="s">
-        <v>15</v>
+      <c r="I148">
+        <v>1</v>
       </c>
       <c r="J148">
         <v>403</v>
@@ -6990,8 +6981,8 @@
       <c r="H149">
         <v>1.4608000000000001</v>
       </c>
-      <c r="I149" t="s">
-        <v>15</v>
+      <c r="I149">
+        <v>1</v>
       </c>
       <c r="J149">
         <v>403</v>
@@ -7034,8 +7025,8 @@
       <c r="H150">
         <v>1.5296000000000001</v>
       </c>
-      <c r="I150" t="s">
-        <v>15</v>
+      <c r="I150">
+        <v>1</v>
       </c>
       <c r="J150">
         <v>403</v>
@@ -7078,8 +7069,8 @@
       <c r="H151">
         <v>1.5257000000000001</v>
       </c>
-      <c r="I151" t="s">
-        <v>15</v>
+      <c r="I151">
+        <v>1</v>
       </c>
       <c r="J151">
         <v>403</v>
@@ -7122,8 +7113,8 @@
       <c r="H152">
         <v>1.6180000000000001</v>
       </c>
-      <c r="I152" t="s">
-        <v>15</v>
+      <c r="I152">
+        <v>1</v>
       </c>
       <c r="J152">
         <v>403</v>
@@ -7166,8 +7157,8 @@
       <c r="H153">
         <v>1.5915999999999999</v>
       </c>
-      <c r="I153" t="s">
-        <v>15</v>
+      <c r="I153">
+        <v>1</v>
       </c>
       <c r="J153">
         <v>403</v>
@@ -7210,8 +7201,8 @@
       <c r="H154">
         <v>1.6102000000000001</v>
       </c>
-      <c r="I154" t="s">
-        <v>15</v>
+      <c r="I154">
+        <v>1</v>
       </c>
       <c r="J154">
         <v>403</v>
@@ -7254,8 +7245,8 @@
       <c r="H155">
         <v>1.6232</v>
       </c>
-      <c r="I155" t="s">
-        <v>15</v>
+      <c r="I155">
+        <v>1</v>
       </c>
       <c r="J155">
         <v>403</v>
@@ -7298,8 +7289,8 @@
       <c r="H156">
         <v>1.7494000000000001</v>
       </c>
-      <c r="I156" t="s">
-        <v>15</v>
+      <c r="I156">
+        <v>1</v>
       </c>
       <c r="J156">
         <v>403</v>
@@ -7342,8 +7333,8 @@
       <c r="H157">
         <v>1.7455000000000001</v>
       </c>
-      <c r="I157" t="s">
-        <v>15</v>
+      <c r="I157">
+        <v>1</v>
       </c>
       <c r="J157">
         <v>403</v>
@@ -7386,8 +7377,8 @@
       <c r="H158">
         <v>1.7363999999999999</v>
       </c>
-      <c r="I158" t="s">
-        <v>15</v>
+      <c r="I158">
+        <v>1</v>
       </c>
       <c r="J158">
         <v>403</v>
@@ -7430,8 +7421,8 @@
       <c r="H159">
         <v>1.8773</v>
       </c>
-      <c r="I159" t="s">
-        <v>15</v>
+      <c r="I159">
+        <v>1</v>
       </c>
       <c r="J159">
         <v>403</v>
@@ -7474,8 +7465,8 @@
       <c r="H160">
         <v>1.7573000000000001</v>
       </c>
-      <c r="I160" t="s">
-        <v>15</v>
+      <c r="I160">
+        <v>1</v>
       </c>
       <c r="J160">
         <v>403</v>
@@ -7518,8 +7509,8 @@
       <c r="H161">
         <v>1.7659</v>
       </c>
-      <c r="I161" t="s">
-        <v>15</v>
+      <c r="I161">
+        <v>1</v>
       </c>
       <c r="J161">
         <v>403</v>
@@ -7562,8 +7553,8 @@
       <c r="H162">
         <v>1.7984</v>
       </c>
-      <c r="I162" t="s">
-        <v>15</v>
+      <c r="I162">
+        <v>1</v>
       </c>
       <c r="J162">
         <v>403</v>
@@ -7606,8 +7597,8 @@
       <c r="H163">
         <v>1.9709000000000001</v>
       </c>
-      <c r="I163" t="s">
-        <v>15</v>
+      <c r="I163">
+        <v>1</v>
       </c>
       <c r="J163">
         <v>403</v>
@@ -7650,8 +7641,8 @@
       <c r="H164">
         <v>2.0407000000000002</v>
       </c>
-      <c r="I164" t="s">
-        <v>15</v>
+      <c r="I164">
+        <v>1</v>
       </c>
       <c r="J164">
         <v>403</v>
@@ -7694,8 +7685,8 @@
       <c r="H165">
         <v>2.1619999999999999</v>
       </c>
-      <c r="I165" t="s">
-        <v>15</v>
+      <c r="I165">
+        <v>1</v>
       </c>
       <c r="J165">
         <v>403</v>
@@ -7738,8 +7729,8 @@
       <c r="H166">
         <v>2.4220000000000002</v>
       </c>
-      <c r="I166" t="s">
-        <v>15</v>
+      <c r="I166">
+        <v>1</v>
       </c>
       <c r="J166">
         <v>403</v>
@@ -7782,8 +7773,8 @@
       <c r="H167">
         <v>2.2833999999999999</v>
       </c>
-      <c r="I167" t="s">
-        <v>15</v>
+      <c r="I167">
+        <v>1</v>
       </c>
       <c r="J167">
         <v>403</v>
@@ -7826,8 +7817,8 @@
       <c r="H168">
         <v>2.0459000000000001</v>
       </c>
-      <c r="I168" t="s">
-        <v>15</v>
+      <c r="I168">
+        <v>1</v>
       </c>
       <c r="J168">
         <v>403</v>
@@ -7870,8 +7861,8 @@
       <c r="H169">
         <v>2.4258999999999999</v>
       </c>
-      <c r="I169" t="s">
-        <v>15</v>
+      <c r="I169">
+        <v>1</v>
       </c>
       <c r="J169">
         <v>403</v>
@@ -7914,8 +7905,8 @@
       <c r="H170">
         <v>2.1</v>
       </c>
-      <c r="I170" t="s">
-        <v>15</v>
+      <c r="I170">
+        <v>1</v>
       </c>
       <c r="J170">
         <v>403</v>
@@ -7958,8 +7949,8 @@
       <c r="H171">
         <v>2.2625000000000002</v>
       </c>
-      <c r="I171" t="s">
-        <v>15</v>
+      <c r="I171">
+        <v>1</v>
       </c>
       <c r="J171">
         <v>403</v>
@@ -8002,8 +7993,8 @@
       <c r="H172">
         <v>2.4258999999999999</v>
       </c>
-      <c r="I172" t="s">
-        <v>15</v>
+      <c r="I172">
+        <v>1</v>
       </c>
       <c r="J172">
         <v>403</v>
@@ -8046,8 +8037,8 @@
       <c r="H173">
         <v>2.3887</v>
       </c>
-      <c r="I173" t="s">
-        <v>15</v>
+      <c r="I173">
+        <v>1</v>
       </c>
       <c r="J173">
         <v>403</v>
@@ -8090,8 +8081,8 @@
       <c r="H174">
         <v>2.5960999999999999</v>
       </c>
-      <c r="I174" t="s">
-        <v>15</v>
+      <c r="I174">
+        <v>1</v>
       </c>
       <c r="J174">
         <v>296</v>
@@ -8134,8 +8125,8 @@
       <c r="H175">
         <v>2.6463000000000001</v>
       </c>
-      <c r="I175" t="s">
-        <v>15</v>
+      <c r="I175">
+        <v>1</v>
       </c>
       <c r="J175">
         <v>296</v>
@@ -8178,8 +8169,8 @@
       <c r="H176">
         <v>2.7019000000000002</v>
       </c>
-      <c r="I176" t="s">
-        <v>15</v>
+      <c r="I176">
+        <v>1</v>
       </c>
       <c r="J176">
         <v>296</v>
@@ -8222,8 +8213,8 @@
       <c r="H177">
         <v>3.1322999999999999</v>
       </c>
-      <c r="I177" t="s">
-        <v>15</v>
+      <c r="I177">
+        <v>1</v>
       </c>
       <c r="J177">
         <v>296</v>
@@ -8266,8 +8257,8 @@
       <c r="H178">
         <v>3.5548999999999999</v>
       </c>
-      <c r="I178" t="s">
-        <v>15</v>
+      <c r="I178">
+        <v>1</v>
       </c>
       <c r="J178">
         <v>296</v>
@@ -8310,8 +8301,8 @@
       <c r="H179">
         <v>3.3174999999999999</v>
       </c>
-      <c r="I179" t="s">
-        <v>15</v>
+      <c r="I179">
+        <v>1</v>
       </c>
       <c r="J179">
         <v>296</v>
@@ -8354,8 +8345,8 @@
       <c r="H180">
         <v>2.9152999999999998</v>
       </c>
-      <c r="I180" t="s">
-        <v>15</v>
+      <c r="I180">
+        <v>1</v>
       </c>
       <c r="J180">
         <v>296</v>
@@ -8398,8 +8389,8 @@
       <c r="H181">
         <v>2.8290000000000002</v>
       </c>
-      <c r="I181" t="s">
-        <v>14</v>
+      <c r="I181">
+        <v>0</v>
       </c>
       <c r="J181">
         <v>193</v>
@@ -8442,8 +8433,8 @@
       <c r="H182">
         <v>2.7410000000000001</v>
       </c>
-      <c r="I182" t="s">
-        <v>14</v>
+      <c r="I182">
+        <v>0</v>
       </c>
       <c r="J182">
         <v>193</v>
@@ -8486,8 +8477,8 @@
       <c r="H183">
         <v>2.5979000000000001</v>
       </c>
-      <c r="I183" t="s">
-        <v>14</v>
+      <c r="I183">
+        <v>0</v>
       </c>
       <c r="J183">
         <v>193</v>
@@ -8530,8 +8521,8 @@
       <c r="H184">
         <v>2.7006000000000001</v>
       </c>
-      <c r="I184" t="s">
-        <v>14</v>
+      <c r="I184">
+        <v>0</v>
       </c>
       <c r="J184">
         <v>193</v>
@@ -8574,8 +8565,8 @@
       <c r="H185">
         <v>2.847</v>
       </c>
-      <c r="I185" t="s">
-        <v>14</v>
+      <c r="I185">
+        <v>0</v>
       </c>
       <c r="J185">
         <v>193</v>
@@ -8618,8 +8609,8 @@
       <c r="H186">
         <v>2.9878999999999998</v>
       </c>
-      <c r="I186" t="s">
-        <v>14</v>
+      <c r="I186">
+        <v>0</v>
       </c>
       <c r="J186">
         <v>193</v>
@@ -8662,8 +8653,8 @@
       <c r="H187">
         <v>3.2797000000000001</v>
       </c>
-      <c r="I187" t="s">
-        <v>14</v>
+      <c r="I187">
+        <v>0</v>
       </c>
       <c r="J187">
         <v>193</v>
@@ -8706,8 +8697,8 @@
       <c r="H188">
         <v>3.1991999999999998</v>
       </c>
-      <c r="I188" t="s">
-        <v>14</v>
+      <c r="I188">
+        <v>0</v>
       </c>
       <c r="J188">
         <v>193</v>
@@ -8750,8 +8741,8 @@
       <c r="H189">
         <v>3.7886000000000002</v>
       </c>
-      <c r="I189" t="s">
-        <v>15</v>
+      <c r="I189">
+        <v>1</v>
       </c>
       <c r="J189">
         <v>398</v>
@@ -8794,8 +8785,8 @@
       <c r="H190">
         <v>4.5667</v>
       </c>
-      <c r="I190" t="s">
-        <v>15</v>
+      <c r="I190">
+        <v>1</v>
       </c>
       <c r="J190">
         <v>398</v>
@@ -8838,8 +8829,8 @@
       <c r="H191">
         <v>4.5667</v>
       </c>
-      <c r="I191" t="s">
-        <v>15</v>
+      <c r="I191">
+        <v>1</v>
       </c>
       <c r="J191">
         <v>398</v>
@@ -8882,8 +8873,8 @@
       <c r="H192">
         <v>6.4798</v>
       </c>
-      <c r="I192" t="s">
-        <v>15</v>
+      <c r="I192">
+        <v>1</v>
       </c>
       <c r="J192">
         <v>398</v>
@@ -8926,8 +8917,8 @@
       <c r="H193">
         <v>6.4798</v>
       </c>
-      <c r="I193" t="s">
-        <v>15</v>
+      <c r="I193">
+        <v>1</v>
       </c>
       <c r="J193">
         <v>398</v>
@@ -8970,8 +8961,8 @@
       <c r="H194">
         <v>6.4798</v>
       </c>
-      <c r="I194" t="s">
-        <v>15</v>
+      <c r="I194">
+        <v>1</v>
       </c>
       <c r="J194">
         <v>398</v>
@@ -9014,8 +9005,8 @@
       <c r="H195">
         <v>6.2195999999999998</v>
       </c>
-      <c r="I195" t="s">
-        <v>14</v>
+      <c r="I195">
+        <v>0</v>
       </c>
       <c r="J195">
         <v>265</v>
@@ -9058,8 +9049,8 @@
       <c r="H196">
         <v>6.2195999999999998</v>
       </c>
-      <c r="I196" t="s">
-        <v>14</v>
+      <c r="I196">
+        <v>0</v>
       </c>
       <c r="J196">
         <v>265</v>
@@ -9102,8 +9093,8 @@
       <c r="H197">
         <v>5.6483999999999996</v>
       </c>
-      <c r="I197" t="s">
-        <v>15</v>
+      <c r="I197">
+        <v>1</v>
       </c>
       <c r="J197">
         <v>255</v>
@@ -9146,8 +9137,8 @@
       <c r="H198">
         <v>7.3090000000000002</v>
       </c>
-      <c r="I198" t="s">
-        <v>14</v>
+      <c r="I198">
+        <v>0</v>
       </c>
       <c r="J198">
         <v>329</v>
@@ -9190,8 +9181,8 @@
       <c r="H199">
         <v>7.3090000000000002</v>
       </c>
-      <c r="I199" t="s">
-        <v>14</v>
+      <c r="I199">
+        <v>0</v>
       </c>
       <c r="J199">
         <v>329</v>
@@ -9234,8 +9225,8 @@
       <c r="H200">
         <v>7.3090000000000002</v>
       </c>
-      <c r="I200" t="s">
-        <v>14</v>
+      <c r="I200">
+        <v>0</v>
       </c>
       <c r="J200">
         <v>329</v>
@@ -9278,8 +9269,8 @@
       <c r="H201">
         <v>7.6534000000000004</v>
       </c>
-      <c r="I201" t="s">
-        <v>14</v>
+      <c r="I201">
+        <v>0</v>
       </c>
       <c r="J201">
         <v>402</v>
@@ -9322,8 +9313,8 @@
       <c r="H202">
         <v>7.6534000000000004</v>
       </c>
-      <c r="I202" t="s">
-        <v>14</v>
+      <c r="I202">
+        <v>0</v>
       </c>
       <c r="J202">
         <v>402</v>
@@ -9366,8 +9357,8 @@
       <c r="H203">
         <v>6.27</v>
       </c>
-      <c r="I203" t="s">
-        <v>14</v>
+      <c r="I203">
+        <v>0</v>
       </c>
       <c r="J203">
         <v>348</v>
@@ -9410,8 +9401,8 @@
       <c r="H204">
         <v>6.27</v>
       </c>
-      <c r="I204" t="s">
-        <v>14</v>
+      <c r="I204">
+        <v>0</v>
       </c>
       <c r="J204">
         <v>348</v>
@@ -9454,8 +9445,8 @@
       <c r="H205">
         <v>5.1180000000000003</v>
       </c>
-      <c r="I205" t="s">
-        <v>15</v>
+      <c r="I205">
+        <v>1</v>
       </c>
       <c r="J205">
         <v>224</v>
@@ -9498,8 +9489,8 @@
       <c r="H206">
         <v>5.1180000000000003</v>
       </c>
-      <c r="I206" t="s">
-        <v>15</v>
+      <c r="I206">
+        <v>1</v>
       </c>
       <c r="J206">
         <v>224</v>
@@ -9542,8 +9533,8 @@
       <c r="H207">
         <v>3.9453999999999998</v>
       </c>
-      <c r="I207" t="s">
-        <v>15</v>
+      <c r="I207">
+        <v>1</v>
       </c>
       <c r="J207">
         <v>277</v>
@@ -9586,8 +9577,8 @@
       <c r="H208">
         <v>4.3548999999999998</v>
       </c>
-      <c r="I208" t="s">
-        <v>15</v>
+      <c r="I208">
+        <v>1</v>
       </c>
       <c r="J208">
         <v>277</v>
@@ -9630,8 +9621,8 @@
       <c r="H209">
         <v>4.3548999999999998</v>
       </c>
-      <c r="I209" t="s">
-        <v>15</v>
+      <c r="I209">
+        <v>1</v>
       </c>
       <c r="J209">
         <v>277</v>
@@ -9674,8 +9665,8 @@
       <c r="H210">
         <v>4.2392000000000003</v>
       </c>
-      <c r="I210" t="s">
-        <v>15</v>
+      <c r="I210">
+        <v>1</v>
       </c>
       <c r="J210">
         <v>277</v>
@@ -9718,8 +9709,8 @@
       <c r="H211">
         <v>3.875</v>
       </c>
-      <c r="I211" t="s">
-        <v>15</v>
+      <c r="I211">
+        <v>1</v>
       </c>
       <c r="J211">
         <v>277</v>
@@ -9762,8 +9753,8 @@
       <c r="H212">
         <v>3.8771</v>
       </c>
-      <c r="I212" t="s">
-        <v>15</v>
+      <c r="I212">
+        <v>1</v>
       </c>
       <c r="J212">
         <v>277</v>
@@ -9806,8 +9797,8 @@
       <c r="H213">
         <v>3.665</v>
       </c>
-      <c r="I213" t="s">
-        <v>15</v>
+      <c r="I213">
+        <v>1</v>
       </c>
       <c r="J213">
         <v>277</v>
@@ -9850,8 +9841,8 @@
       <c r="H214">
         <v>3.6526000000000001</v>
       </c>
-      <c r="I214" t="s">
-        <v>15</v>
+      <c r="I214">
+        <v>1</v>
       </c>
       <c r="J214">
         <v>277</v>
@@ -9894,8 +9885,8 @@
       <c r="H215">
         <v>3.9453999999999998</v>
       </c>
-      <c r="I215" t="s">
-        <v>15</v>
+      <c r="I215">
+        <v>1</v>
       </c>
       <c r="J215">
         <v>277</v>
@@ -9938,8 +9929,8 @@
       <c r="H216">
         <v>3.5874999999999999</v>
       </c>
-      <c r="I216" t="s">
-        <v>15</v>
+      <c r="I216">
+        <v>1</v>
       </c>
       <c r="J216">
         <v>277</v>
@@ -9982,8 +9973,8 @@
       <c r="H217">
         <v>3.9453999999999998</v>
       </c>
-      <c r="I217" t="s">
-        <v>15</v>
+      <c r="I217">
+        <v>1</v>
       </c>
       <c r="J217">
         <v>277</v>
@@ -10026,8 +10017,8 @@
       <c r="H218">
         <v>3.1120999999999999</v>
       </c>
-      <c r="I218" t="s">
-        <v>15</v>
+      <c r="I218">
+        <v>1</v>
       </c>
       <c r="J218">
         <v>276</v>
@@ -10070,8 +10061,8 @@
       <c r="H219">
         <v>3.4211</v>
       </c>
-      <c r="I219" t="s">
-        <v>15</v>
+      <c r="I219">
+        <v>1</v>
       </c>
       <c r="J219">
         <v>276</v>
@@ -10114,8 +10105,8 @@
       <c r="H220">
         <v>2.8893</v>
       </c>
-      <c r="I220" t="s">
-        <v>15</v>
+      <c r="I220">
+        <v>1</v>
       </c>
       <c r="J220">
         <v>276</v>
@@ -10158,8 +10149,8 @@
       <c r="H221">
         <v>3.3633000000000002</v>
       </c>
-      <c r="I221" t="s">
-        <v>15</v>
+      <c r="I221">
+        <v>1</v>
       </c>
       <c r="J221">
         <v>276</v>
@@ -10202,8 +10193,8 @@
       <c r="H222">
         <v>2.8616999999999999</v>
       </c>
-      <c r="I222" t="s">
-        <v>16</v>
+      <c r="I222">
+        <v>2</v>
       </c>
       <c r="J222">
         <v>307</v>
@@ -10246,8 +10237,8 @@
       <c r="H223">
         <v>3.048</v>
       </c>
-      <c r="I223" t="s">
-        <v>16</v>
+      <c r="I223">
+        <v>2</v>
       </c>
       <c r="J223">
         <v>307</v>
@@ -10290,8 +10281,8 @@
       <c r="H224">
         <v>3.2721</v>
       </c>
-      <c r="I224" t="s">
-        <v>16</v>
+      <c r="I224">
+        <v>2</v>
       </c>
       <c r="J224">
         <v>307</v>
@@ -10334,8 +10325,8 @@
       <c r="H225">
         <v>3.2721</v>
       </c>
-      <c r="I225" t="s">
-        <v>16</v>
+      <c r="I225">
+        <v>2</v>
       </c>
       <c r="J225">
         <v>307</v>
@@ -10378,8 +10369,8 @@
       <c r="H226">
         <v>2.8944000000000001</v>
       </c>
-      <c r="I226" t="s">
-        <v>16</v>
+      <c r="I226">
+        <v>2</v>
       </c>
       <c r="J226">
         <v>307</v>
@@ -10422,8 +10413,8 @@
       <c r="H227">
         <v>2.8944000000000001</v>
       </c>
-      <c r="I227" t="s">
-        <v>16</v>
+      <c r="I227">
+        <v>2</v>
       </c>
       <c r="J227">
         <v>307</v>
@@ -10466,8 +10457,8 @@
       <c r="H228">
         <v>3.2157</v>
       </c>
-      <c r="I228" t="s">
-        <v>16</v>
+      <c r="I228">
+        <v>2</v>
       </c>
       <c r="J228">
         <v>307</v>
@@ -10510,8 +10501,8 @@
       <c r="H229">
         <v>3.2157</v>
       </c>
-      <c r="I229" t="s">
-        <v>16</v>
+      <c r="I229">
+        <v>2</v>
       </c>
       <c r="J229">
         <v>307</v>
@@ -10554,8 +10545,8 @@
       <c r="H230">
         <v>3.3751000000000002</v>
       </c>
-      <c r="I230" t="s">
-        <v>16</v>
+      <c r="I230">
+        <v>2</v>
       </c>
       <c r="J230">
         <v>307</v>
@@ -10598,8 +10589,8 @@
       <c r="H231">
         <v>3.3751000000000002</v>
       </c>
-      <c r="I231" t="s">
-        <v>16</v>
+      <c r="I231">
+        <v>2</v>
       </c>
       <c r="J231">
         <v>307</v>
@@ -10642,8 +10633,8 @@
       <c r="H232">
         <v>3.6715</v>
       </c>
-      <c r="I232" t="s">
-        <v>16</v>
+      <c r="I232">
+        <v>2</v>
       </c>
       <c r="J232">
         <v>307</v>
@@ -10686,8 +10677,8 @@
       <c r="H233">
         <v>3.6715</v>
       </c>
-      <c r="I233" t="s">
-        <v>16</v>
+      <c r="I233">
+        <v>2</v>
       </c>
       <c r="J233">
         <v>307</v>
@@ -10730,8 +10721,8 @@
       <c r="H234">
         <v>3.8384</v>
       </c>
-      <c r="I234" t="s">
-        <v>16</v>
+      <c r="I234">
+        <v>2</v>
       </c>
       <c r="J234">
         <v>307</v>
@@ -10774,8 +10765,8 @@
       <c r="H235">
         <v>3.6518999999999999</v>
       </c>
-      <c r="I235" t="s">
-        <v>16</v>
+      <c r="I235">
+        <v>2</v>
       </c>
       <c r="J235">
         <v>307</v>
@@ -10818,8 +10809,8 @@
       <c r="H236">
         <v>3.6518999999999999</v>
       </c>
-      <c r="I236" t="s">
-        <v>16</v>
+      <c r="I236">
+        <v>2</v>
       </c>
       <c r="J236">
         <v>307</v>
@@ -10862,8 +10853,8 @@
       <c r="H237">
         <v>3.6518999999999999</v>
       </c>
-      <c r="I237" t="s">
-        <v>16</v>
+      <c r="I237">
+        <v>2</v>
       </c>
       <c r="J237">
         <v>307</v>
@@ -10906,8 +10897,8 @@
       <c r="H238">
         <v>4.1479999999999997</v>
       </c>
-      <c r="I238" t="s">
-        <v>16</v>
+      <c r="I238">
+        <v>2</v>
       </c>
       <c r="J238">
         <v>307</v>
@@ -10950,8 +10941,8 @@
       <c r="H239">
         <v>4.1479999999999997</v>
       </c>
-      <c r="I239" t="s">
-        <v>16</v>
+      <c r="I239">
+        <v>2</v>
       </c>
       <c r="J239">
         <v>307</v>
@@ -10994,8 +10985,8 @@
       <c r="H240">
         <v>6.1898999999999997</v>
       </c>
-      <c r="I240" t="s">
-        <v>15</v>
+      <c r="I240">
+        <v>1</v>
       </c>
       <c r="J240">
         <v>300</v>
@@ -11038,8 +11029,8 @@
       <c r="H241">
         <v>6.1898999999999997</v>
       </c>
-      <c r="I241" t="s">
-        <v>15</v>
+      <c r="I241">
+        <v>1</v>
       </c>
       <c r="J241">
         <v>300</v>
@@ -11082,8 +11073,8 @@
       <c r="H242">
         <v>6.3361000000000001</v>
       </c>
-      <c r="I242" t="s">
-        <v>15</v>
+      <c r="I242">
+        <v>1</v>
       </c>
       <c r="J242">
         <v>300</v>
@@ -11126,8 +11117,8 @@
       <c r="H243">
         <v>6.3361000000000001</v>
       </c>
-      <c r="I243" t="s">
-        <v>15</v>
+      <c r="I243">
+        <v>1</v>
       </c>
       <c r="J243">
         <v>300</v>
@@ -11170,8 +11161,8 @@
       <c r="H244">
         <v>7.0354999999999999</v>
       </c>
-      <c r="I244" t="s">
-        <v>15</v>
+      <c r="I244">
+        <v>1</v>
       </c>
       <c r="J244">
         <v>300</v>
@@ -11214,8 +11205,8 @@
       <c r="H245">
         <v>7.0354999999999999</v>
       </c>
-      <c r="I245" t="s">
-        <v>15</v>
+      <c r="I245">
+        <v>1</v>
       </c>
       <c r="J245">
         <v>300</v>
@@ -11258,8 +11249,8 @@
       <c r="H246">
         <v>7.9549000000000003</v>
       </c>
-      <c r="I246" t="s">
-        <v>16</v>
+      <c r="I246">
+        <v>2</v>
       </c>
       <c r="J246">
         <v>330</v>
@@ -11302,8 +11293,8 @@
       <c r="H247">
         <v>7.9549000000000003</v>
       </c>
-      <c r="I247" t="s">
-        <v>16</v>
+      <c r="I247">
+        <v>2</v>
       </c>
       <c r="J247">
         <v>330</v>
@@ -11346,8 +11337,8 @@
       <c r="H248">
         <v>8.0555000000000003</v>
       </c>
-      <c r="I248" t="s">
-        <v>16</v>
+      <c r="I248">
+        <v>2</v>
       </c>
       <c r="J248">
         <v>330</v>
@@ -11390,8 +11381,8 @@
       <c r="H249">
         <v>8.0555000000000003</v>
       </c>
-      <c r="I249" t="s">
-        <v>16</v>
+      <c r="I249">
+        <v>2</v>
       </c>
       <c r="J249">
         <v>330</v>
@@ -11434,8 +11425,8 @@
       <c r="H250">
         <v>7.8265000000000002</v>
       </c>
-      <c r="I250" t="s">
-        <v>16</v>
+      <c r="I250">
+        <v>2</v>
       </c>
       <c r="J250">
         <v>330</v>
@@ -11478,8 +11469,8 @@
       <c r="H251">
         <v>7.8265000000000002</v>
       </c>
-      <c r="I251" t="s">
-        <v>16</v>
+      <c r="I251">
+        <v>2</v>
       </c>
       <c r="J251">
         <v>330</v>
@@ -11522,8 +11513,8 @@
       <c r="H252">
         <v>7.3967000000000001</v>
       </c>
-      <c r="I252" t="s">
-        <v>16</v>
+      <c r="I252">
+        <v>2</v>
       </c>
       <c r="J252">
         <v>330</v>
@@ -11566,8 +11557,8 @@
       <c r="H253">
         <v>7.3967000000000001</v>
       </c>
-      <c r="I253" t="s">
-        <v>16</v>
+      <c r="I253">
+        <v>2</v>
       </c>
       <c r="J253">
         <v>330</v>
@@ -11610,8 +11601,8 @@
       <c r="H254">
         <v>8.9067000000000007</v>
       </c>
-      <c r="I254" t="s">
-        <v>16</v>
+      <c r="I254">
+        <v>2</v>
       </c>
       <c r="J254">
         <v>330</v>
@@ -11654,8 +11645,8 @@
       <c r="H255">
         <v>8.9067000000000007</v>
       </c>
-      <c r="I255" t="s">
-        <v>16</v>
+      <c r="I255">
+        <v>2</v>
       </c>
       <c r="J255">
         <v>330</v>
@@ -11698,8 +11689,8 @@
       <c r="H256">
         <v>9.2202999999999999</v>
       </c>
-      <c r="I256" t="s">
-        <v>14</v>
+      <c r="I256">
+        <v>0</v>
       </c>
       <c r="J256">
         <v>315</v>
@@ -11742,8 +11733,8 @@
       <c r="H257">
         <v>9.2202999999999999</v>
       </c>
-      <c r="I257" t="s">
-        <v>14</v>
+      <c r="I257">
+        <v>0</v>
       </c>
       <c r="J257">
         <v>315</v>
@@ -11786,8 +11777,8 @@
       <c r="H258">
         <v>6.3361000000000001</v>
       </c>
-      <c r="I258" t="s">
-        <v>14</v>
+      <c r="I258">
+        <v>0</v>
       </c>
       <c r="J258">
         <v>244</v>
@@ -11830,8 +11821,8 @@
       <c r="H259">
         <v>1.8009999999999999</v>
       </c>
-      <c r="I259" t="s">
-        <v>15</v>
+      <c r="I259">
+        <v>1</v>
       </c>
       <c r="J259">
         <v>264</v>
@@ -11874,8 +11865,8 @@
       <c r="H260">
         <v>1.8946000000000001</v>
       </c>
-      <c r="I260" t="s">
-        <v>15</v>
+      <c r="I260">
+        <v>1</v>
       </c>
       <c r="J260">
         <v>264</v>
@@ -11918,8 +11909,8 @@
       <c r="H261">
         <v>2.0106999999999999</v>
       </c>
-      <c r="I261" t="s">
-        <v>15</v>
+      <c r="I261">
+        <v>1</v>
       </c>
       <c r="J261">
         <v>264</v>
@@ -11962,8 +11953,8 @@
       <c r="H262">
         <v>2.1120999999999999</v>
       </c>
-      <c r="I262" t="s">
-        <v>15</v>
+      <c r="I262">
+        <v>1</v>
       </c>
       <c r="J262">
         <v>264</v>
@@ -12006,8 +11997,8 @@
       <c r="H263">
         <v>2.1398000000000001</v>
       </c>
-      <c r="I263" t="s">
-        <v>15</v>
+      <c r="I263">
+        <v>1</v>
       </c>
       <c r="J263">
         <v>264</v>
@@ -12050,8 +12041,8 @@
       <c r="H264">
         <v>2.2885</v>
       </c>
-      <c r="I264" t="s">
-        <v>15</v>
+      <c r="I264">
+        <v>1</v>
       </c>
       <c r="J264">
         <v>264</v>
@@ -12094,8 +12085,8 @@
       <c r="H265">
         <v>2.0788000000000002</v>
       </c>
-      <c r="I265" t="s">
-        <v>15</v>
+      <c r="I265">
+        <v>1</v>
       </c>
       <c r="J265">
         <v>264</v>
@@ -12138,8 +12129,8 @@
       <c r="H266">
         <v>1.9300999999999999</v>
       </c>
-      <c r="I266" t="s">
-        <v>15</v>
+      <c r="I266">
+        <v>1</v>
       </c>
       <c r="J266">
         <v>264</v>
@@ -12182,8 +12173,8 @@
       <c r="H267">
         <v>1.9864999999999999</v>
       </c>
-      <c r="I267" t="s">
-        <v>15</v>
+      <c r="I267">
+        <v>1</v>
       </c>
       <c r="J267">
         <v>264</v>
@@ -12226,8 +12217,8 @@
       <c r="H268">
         <v>2.1328999999999998</v>
       </c>
-      <c r="I268" t="s">
-        <v>15</v>
+      <c r="I268">
+        <v>1</v>
       </c>
       <c r="J268">
         <v>264</v>
@@ -12270,8 +12261,8 @@
       <c r="H269">
         <v>2.4216000000000002</v>
       </c>
-      <c r="I269" t="s">
-        <v>15</v>
+      <c r="I269">
+        <v>1</v>
       </c>
       <c r="J269">
         <v>264</v>
@@ -12314,8 +12305,8 @@
       <c r="H270">
         <v>2.8719999999999999</v>
       </c>
-      <c r="I270" t="s">
-        <v>15</v>
+      <c r="I270">
+        <v>1</v>
       </c>
       <c r="J270">
         <v>264</v>
@@ -12358,8 +12349,8 @@
       <c r="H271">
         <v>3.9175</v>
       </c>
-      <c r="I271" t="s">
-        <v>14</v>
+      <c r="I271">
+        <v>0</v>
       </c>
       <c r="J271">
         <v>223</v>
@@ -12402,8 +12393,8 @@
       <c r="H272">
         <v>4.4290000000000003</v>
       </c>
-      <c r="I272" t="s">
-        <v>14</v>
+      <c r="I272">
+        <v>0</v>
       </c>
       <c r="J272">
         <v>223</v>
@@ -12446,8 +12437,8 @@
       <c r="H273">
         <v>4.4290000000000003</v>
       </c>
-      <c r="I273" t="s">
-        <v>14</v>
+      <c r="I273">
+        <v>0</v>
       </c>
       <c r="J273">
         <v>223</v>
@@ -12490,8 +12481,8 @@
       <c r="H274">
         <v>3.9175</v>
       </c>
-      <c r="I274" t="s">
-        <v>14</v>
+      <c r="I274">
+        <v>0</v>
       </c>
       <c r="J274">
         <v>223</v>
@@ -12534,8 +12525,8 @@
       <c r="H275">
         <v>4.3665000000000003</v>
       </c>
-      <c r="I275" t="s">
-        <v>14</v>
+      <c r="I275">
+        <v>0</v>
       </c>
       <c r="J275">
         <v>223</v>
@@ -12578,8 +12569,8 @@
       <c r="H276">
         <v>4.0776000000000003</v>
       </c>
-      <c r="I276" t="s">
-        <v>15</v>
+      <c r="I276">
+        <v>1</v>
       </c>
       <c r="J276">
         <v>254</v>
@@ -12622,8 +12613,8 @@
       <c r="H277">
         <v>4.2672999999999996</v>
       </c>
-      <c r="I277" t="s">
-        <v>15</v>
+      <c r="I277">
+        <v>1</v>
       </c>
       <c r="J277">
         <v>254</v>
@@ -12666,8 +12657,8 @@
       <c r="H278">
         <v>4.7872000000000003</v>
       </c>
-      <c r="I278" t="s">
-        <v>15</v>
+      <c r="I278">
+        <v>1</v>
       </c>
       <c r="J278">
         <v>254</v>
@@ -12710,8 +12701,8 @@
       <c r="H279">
         <v>4.8628</v>
       </c>
-      <c r="I279" t="s">
-        <v>15</v>
+      <c r="I279">
+        <v>1</v>
       </c>
       <c r="J279">
         <v>254</v>
@@ -12754,8 +12745,8 @@
       <c r="H280">
         <v>4.1402999999999999</v>
       </c>
-      <c r="I280" t="s">
-        <v>15</v>
+      <c r="I280">
+        <v>1</v>
       </c>
       <c r="J280">
         <v>254</v>
@@ -12798,8 +12789,8 @@
       <c r="H281">
         <v>4.1006999999999998</v>
       </c>
-      <c r="I281" t="s">
-        <v>15</v>
+      <c r="I281">
+        <v>1</v>
       </c>
       <c r="J281">
         <v>216</v>
@@ -12842,8 +12833,8 @@
       <c r="H282">
         <v>4.6947000000000001</v>
       </c>
-      <c r="I282" t="s">
-        <v>15</v>
+      <c r="I282">
+        <v>1</v>
       </c>
       <c r="J282">
         <v>216</v>
@@ -12886,8 +12877,8 @@
       <c r="H283">
         <v>5.2446999999999999</v>
       </c>
-      <c r="I283" t="s">
-        <v>15</v>
+      <c r="I283">
+        <v>1</v>
       </c>
       <c r="J283">
         <v>216</v>
@@ -12930,8 +12921,8 @@
       <c r="H284">
         <v>5.2119</v>
       </c>
-      <c r="I284" t="s">
-        <v>15</v>
+      <c r="I284">
+        <v>1</v>
       </c>
       <c r="J284">
         <v>216</v>
@@ -12974,8 +12965,8 @@
       <c r="H285">
         <v>5.8849999999999998</v>
       </c>
-      <c r="I285" t="s">
-        <v>14</v>
+      <c r="I285">
+        <v>0</v>
       </c>
       <c r="J285">
         <v>198</v>
@@ -13018,8 +13009,8 @@
       <c r="H286">
         <v>7.3072999999999997</v>
       </c>
-      <c r="I286" t="s">
-        <v>14</v>
+      <c r="I286">
+        <v>0</v>
       </c>
       <c r="J286">
         <v>285</v>
@@ -13062,8 +13053,8 @@
       <c r="H287">
         <v>7.3072999999999997</v>
       </c>
-      <c r="I287" t="s">
-        <v>14</v>
+      <c r="I287">
+        <v>0</v>
       </c>
       <c r="J287">
         <v>300</v>
@@ -13106,8 +13097,8 @@
       <c r="H288">
         <v>9.0891999999999999</v>
       </c>
-      <c r="I288" t="s">
-        <v>14</v>
+      <c r="I288">
+        <v>0</v>
       </c>
       <c r="J288">
         <v>241</v>
@@ -13150,8 +13141,8 @@
       <c r="H289">
         <v>7.3171999999999997</v>
       </c>
-      <c r="I289" t="s">
-        <v>15</v>
+      <c r="I289">
+        <v>1</v>
       </c>
       <c r="J289">
         <v>293</v>
@@ -13194,8 +13185,8 @@
       <c r="H290">
         <v>7.3171999999999997</v>
       </c>
-      <c r="I290" t="s">
-        <v>15</v>
+      <c r="I290">
+        <v>1</v>
       </c>
       <c r="J290">
         <v>293</v>
@@ -13238,8 +13229,8 @@
       <c r="H291">
         <v>7.3171999999999997</v>
       </c>
-      <c r="I291" t="s">
-        <v>15</v>
+      <c r="I291">
+        <v>1</v>
       </c>
       <c r="J291">
         <v>293</v>
@@ -13282,8 +13273,8 @@
       <c r="H292">
         <v>5.1166999999999998</v>
       </c>
-      <c r="I292" t="s">
-        <v>15</v>
+      <c r="I292">
+        <v>1</v>
       </c>
       <c r="J292">
         <v>245</v>
@@ -13326,8 +13317,8 @@
       <c r="H293">
         <v>5.1166999999999998</v>
       </c>
-      <c r="I293" t="s">
-        <v>15</v>
+      <c r="I293">
+        <v>1</v>
       </c>
       <c r="J293">
         <v>245</v>
@@ -13370,8 +13361,8 @@
       <c r="H294">
         <v>5.1166999999999998</v>
       </c>
-      <c r="I294" t="s">
-        <v>15</v>
+      <c r="I294">
+        <v>1</v>
       </c>
       <c r="J294">
         <v>245</v>
@@ -13414,8 +13405,8 @@
       <c r="H295">
         <v>5.5026999999999999</v>
       </c>
-      <c r="I295" t="s">
-        <v>15</v>
+      <c r="I295">
+        <v>1</v>
       </c>
       <c r="J295">
         <v>289</v>
@@ -13458,8 +13449,8 @@
       <c r="H296">
         <v>5.5026999999999999</v>
       </c>
-      <c r="I296" t="s">
-        <v>15</v>
+      <c r="I296">
+        <v>1</v>
       </c>
       <c r="J296">
         <v>289</v>
@@ -13502,8 +13493,8 @@
       <c r="H297">
         <v>5.9603999999999999</v>
       </c>
-      <c r="I297" t="s">
-        <v>15</v>
+      <c r="I297">
+        <v>1</v>
       </c>
       <c r="J297">
         <v>289</v>
@@ -13546,8 +13537,8 @@
       <c r="H298">
         <v>5.9603999999999999</v>
       </c>
-      <c r="I298" t="s">
-        <v>15</v>
+      <c r="I298">
+        <v>1</v>
       </c>
       <c r="J298">
         <v>289</v>
@@ -13590,8 +13581,8 @@
       <c r="H299">
         <v>6.32</v>
       </c>
-      <c r="I299" t="s">
-        <v>15</v>
+      <c r="I299">
+        <v>1</v>
       </c>
       <c r="J299">
         <v>289</v>
@@ -13634,8 +13625,8 @@
       <c r="H300">
         <v>7.8277999999999999</v>
       </c>
-      <c r="I300" t="s">
-        <v>15</v>
+      <c r="I300">
+        <v>1</v>
       </c>
       <c r="J300">
         <v>358</v>
@@ -13678,8 +13669,8 @@
       <c r="H301">
         <v>7.8277999999999999</v>
       </c>
-      <c r="I301" t="s">
-        <v>15</v>
+      <c r="I301">
+        <v>1</v>
       </c>
       <c r="J301">
         <v>358</v>
@@ -13722,8 +13713,8 @@
       <c r="H302">
         <v>7.8277999999999999</v>
       </c>
-      <c r="I302" t="s">
-        <v>15</v>
+      <c r="I302">
+        <v>1</v>
       </c>
       <c r="J302">
         <v>358</v>
@@ -13766,8 +13757,8 @@
       <c r="H303">
         <v>5.4916999999999998</v>
       </c>
-      <c r="I303" t="s">
-        <v>16</v>
+      <c r="I303">
+        <v>2</v>
       </c>
       <c r="J303">
         <v>329</v>
@@ -13810,8 +13801,8 @@
       <c r="H304">
         <v>5.4916999999999998</v>
       </c>
-      <c r="I304" t="s">
-        <v>16</v>
+      <c r="I304">
+        <v>2</v>
       </c>
       <c r="J304">
         <v>329</v>
@@ -13854,8 +13845,8 @@
       <c r="H305">
         <v>5.4916999999999998</v>
       </c>
-      <c r="I305" t="s">
-        <v>16</v>
+      <c r="I305">
+        <v>2</v>
       </c>
       <c r="J305">
         <v>329</v>
@@ -13898,8 +13889,8 @@
       <c r="H306">
         <v>4.0220000000000002</v>
       </c>
-      <c r="I306" t="s">
-        <v>16</v>
+      <c r="I306">
+        <v>2</v>
       </c>
       <c r="J306">
         <v>222</v>
@@ -13942,8 +13933,8 @@
       <c r="H307">
         <v>3.37</v>
       </c>
-      <c r="I307" t="s">
-        <v>16</v>
+      <c r="I307">
+        <v>2</v>
       </c>
       <c r="J307">
         <v>222</v>
@@ -13986,8 +13977,8 @@
       <c r="H308">
         <v>3.0992000000000002</v>
       </c>
-      <c r="I308" t="s">
-        <v>16</v>
+      <c r="I308">
+        <v>2</v>
       </c>
       <c r="J308">
         <v>222</v>
@@ -14030,8 +14021,8 @@
       <c r="H309">
         <v>3.1827000000000001</v>
       </c>
-      <c r="I309" t="s">
-        <v>16</v>
+      <c r="I309">
+        <v>2</v>
       </c>
       <c r="J309">
         <v>222</v>
@@ -14074,8 +14065,8 @@
       <c r="H310">
         <v>3.3174999999999999</v>
       </c>
-      <c r="I310" t="s">
-        <v>15</v>
+      <c r="I310">
+        <v>1</v>
       </c>
       <c r="J310">
         <v>304</v>
@@ -14118,8 +14109,8 @@
       <c r="H311">
         <v>3.1025</v>
       </c>
-      <c r="I311" t="s">
-        <v>15</v>
+      <c r="I311">
+        <v>1</v>
       </c>
       <c r="J311">
         <v>304</v>
@@ -14162,8 +14153,8 @@
       <c r="H312">
         <v>2.5194000000000001</v>
       </c>
-      <c r="I312" t="s">
-        <v>15</v>
+      <c r="I312">
+        <v>1</v>
       </c>
       <c r="J312">
         <v>304</v>
@@ -14206,8 +14197,8 @@
       <c r="H313">
         <v>2.6402999999999999</v>
       </c>
-      <c r="I313" t="s">
-        <v>15</v>
+      <c r="I313">
+        <v>1</v>
       </c>
       <c r="J313">
         <v>304</v>
@@ -14250,8 +14241,8 @@
       <c r="H314">
         <v>2.8340000000000001</v>
       </c>
-      <c r="I314" t="s">
-        <v>15</v>
+      <c r="I314">
+        <v>1</v>
       </c>
       <c r="J314">
         <v>304</v>
@@ -14294,8 +14285,8 @@
       <c r="H315">
         <v>3.2627999999999999</v>
       </c>
-      <c r="I315" t="s">
-        <v>15</v>
+      <c r="I315">
+        <v>1</v>
       </c>
       <c r="J315">
         <v>304</v>
@@ -14338,8 +14329,8 @@
       <c r="H316">
         <v>3.6023000000000001</v>
       </c>
-      <c r="I316" t="s">
-        <v>15</v>
+      <c r="I316">
+        <v>1</v>
       </c>
       <c r="J316">
         <v>304</v>
@@ -14382,8 +14373,8 @@
       <c r="H317">
         <v>3.9449999999999998</v>
       </c>
-      <c r="I317" t="s">
-        <v>15</v>
+      <c r="I317">
+        <v>1</v>
       </c>
       <c r="J317">
         <v>304</v>
@@ -14426,8 +14417,8 @@
       <c r="H318">
         <v>3.9986000000000002</v>
       </c>
-      <c r="I318" t="s">
-        <v>15</v>
+      <c r="I318">
+        <v>1</v>
       </c>
       <c r="J318">
         <v>304</v>
@@ -14470,8 +14461,8 @@
       <c r="H319">
         <v>4.0316999999999998</v>
       </c>
-      <c r="I319" t="s">
-        <v>15</v>
+      <c r="I319">
+        <v>1</v>
       </c>
       <c r="J319">
         <v>304</v>
@@ -14514,8 +14505,8 @@
       <c r="H320">
         <v>3.5325000000000002</v>
       </c>
-      <c r="I320" t="s">
-        <v>15</v>
+      <c r="I320">
+        <v>1</v>
       </c>
       <c r="J320">
         <v>304</v>
@@ -14558,8 +14549,8 @@
       <c r="H321">
         <v>4.0019</v>
       </c>
-      <c r="I321" t="s">
-        <v>15</v>
+      <c r="I321">
+        <v>1</v>
       </c>
       <c r="J321">
         <v>304</v>
@@ -14602,8 +14593,8 @@
       <c r="H322">
         <v>4.5404</v>
       </c>
-      <c r="I322" t="s">
-        <v>15</v>
+      <c r="I322">
+        <v>1</v>
       </c>
       <c r="J322">
         <v>287</v>
@@ -14646,8 +14637,8 @@
       <c r="H323">
         <v>4.5404</v>
       </c>
-      <c r="I323" t="s">
-        <v>15</v>
+      <c r="I323">
+        <v>1</v>
       </c>
       <c r="J323">
         <v>287</v>
@@ -14690,8 +14681,8 @@
       <c r="H324">
         <v>4.7210999999999999</v>
       </c>
-      <c r="I324" t="s">
-        <v>15</v>
+      <c r="I324">
+        <v>1</v>
       </c>
       <c r="J324">
         <v>287</v>
@@ -14734,8 +14725,8 @@
       <c r="H325">
         <v>4.7210999999999999</v>
       </c>
-      <c r="I325" t="s">
-        <v>15</v>
+      <c r="I325">
+        <v>1</v>
       </c>
       <c r="J325">
         <v>287</v>
@@ -14778,8 +14769,8 @@
       <c r="H326">
         <v>4.7210999999999999</v>
       </c>
-      <c r="I326" t="s">
-        <v>15</v>
+      <c r="I326">
+        <v>1</v>
       </c>
       <c r="J326">
         <v>287</v>
@@ -14822,8 +14813,8 @@
       <c r="H327">
         <v>5.4158999999999997</v>
       </c>
-      <c r="I327" t="s">
-        <v>15</v>
+      <c r="I327">
+        <v>1</v>
       </c>
       <c r="J327">
         <v>287</v>
@@ -14866,8 +14857,8 @@
       <c r="H328">
         <v>5.4158999999999997</v>
       </c>
-      <c r="I328" t="s">
-        <v>15</v>
+      <c r="I328">
+        <v>1</v>
       </c>
       <c r="J328">
         <v>287</v>
@@ -14910,8 +14901,8 @@
       <c r="H329">
         <v>5.4158999999999997</v>
       </c>
-      <c r="I329" t="s">
-        <v>15</v>
+      <c r="I329">
+        <v>1</v>
       </c>
       <c r="J329">
         <v>287</v>
@@ -14954,8 +14945,8 @@
       <c r="H330">
         <v>5.2145999999999999</v>
       </c>
-      <c r="I330" t="s">
-        <v>15</v>
+      <c r="I330">
+        <v>1</v>
       </c>
       <c r="J330">
         <v>430</v>
@@ -14998,8 +14989,8 @@
       <c r="H331">
         <v>5.2145999999999999</v>
       </c>
-      <c r="I331" t="s">
-        <v>15</v>
+      <c r="I331">
+        <v>1</v>
       </c>
       <c r="J331">
         <v>430</v>
@@ -15042,8 +15033,8 @@
       <c r="H332">
         <v>5.8735999999999997</v>
       </c>
-      <c r="I332" t="s">
-        <v>15</v>
+      <c r="I332">
+        <v>1</v>
       </c>
       <c r="J332">
         <v>430</v>
@@ -15086,8 +15077,8 @@
       <c r="H333">
         <v>6.6406999999999998</v>
       </c>
-      <c r="I333" t="s">
-        <v>14</v>
+      <c r="I333">
+        <v>0</v>
       </c>
       <c r="J333">
         <v>304</v>
@@ -15130,8 +15121,8 @@
       <c r="H334">
         <v>6.6406999999999998</v>
       </c>
-      <c r="I334" t="s">
-        <v>14</v>
+      <c r="I334">
+        <v>0</v>
       </c>
       <c r="J334">
         <v>304</v>
@@ -15174,8 +15165,8 @@
       <c r="H335">
         <v>6.4584000000000001</v>
       </c>
-      <c r="I335" t="s">
-        <v>15</v>
+      <c r="I335">
+        <v>1</v>
       </c>
       <c r="J335">
         <v>224</v>
@@ -15218,8 +15209,8 @@
       <c r="H336">
         <v>6.4584000000000001</v>
       </c>
-      <c r="I336" t="s">
-        <v>15</v>
+      <c r="I336">
+        <v>1</v>
       </c>
       <c r="J336">
         <v>224</v>
@@ -15262,8 +15253,8 @@
       <c r="H337">
         <v>5.9852999999999996</v>
       </c>
-      <c r="I337" t="s">
-        <v>15</v>
+      <c r="I337">
+        <v>1</v>
       </c>
       <c r="J337">
         <v>224</v>
@@ -15306,8 +15297,8 @@
       <c r="H338">
         <v>5.2310999999999996</v>
       </c>
-      <c r="I338" t="s">
-        <v>15</v>
+      <c r="I338">
+        <v>1</v>
       </c>
       <c r="J338">
         <v>224</v>
@@ -15350,8 +15341,8 @@
       <c r="H339">
         <v>5.6150000000000002</v>
       </c>
-      <c r="I339" t="s">
-        <v>15</v>
+      <c r="I339">
+        <v>1</v>
       </c>
       <c r="J339">
         <v>224</v>
@@ -15394,8 +15385,8 @@
       <c r="H340">
         <v>4.8121999999999998</v>
       </c>
-      <c r="I340" t="s">
-        <v>15</v>
+      <c r="I340">
+        <v>1</v>
       </c>
       <c r="J340">
         <v>224</v>
@@ -15438,8 +15429,8 @@
       <c r="H341">
         <v>4.8121999999999998</v>
       </c>
-      <c r="I341" t="s">
-        <v>15</v>
+      <c r="I341">
+        <v>1</v>
       </c>
       <c r="J341">
         <v>224</v>
@@ -15482,8 +15473,8 @@
       <c r="H342">
         <v>4.8121999999999998</v>
       </c>
-      <c r="I342" t="s">
-        <v>15</v>
+      <c r="I342">
+        <v>1</v>
       </c>
       <c r="J342">
         <v>224</v>
@@ -15526,8 +15517,8 @@
       <c r="H343">
         <v>7.0378999999999996</v>
       </c>
-      <c r="I343" t="s">
-        <v>14</v>
+      <c r="I343">
+        <v>0</v>
       </c>
       <c r="J343">
         <v>284</v>
@@ -15570,8 +15561,8 @@
       <c r="H344">
         <v>6.2668999999999997</v>
       </c>
-      <c r="I344" t="s">
-        <v>14</v>
+      <c r="I344">
+        <v>0</v>
       </c>
       <c r="J344">
         <v>422</v>
@@ -15614,8 +15605,8 @@
       <c r="H345">
         <v>5.7321</v>
       </c>
-      <c r="I345" t="s">
-        <v>15</v>
+      <c r="I345">
+        <v>1</v>
       </c>
       <c r="J345">
         <v>370</v>
@@ -15658,8 +15649,8 @@
       <c r="H346">
         <v>6.4653999999999998</v>
       </c>
-      <c r="I346" t="s">
-        <v>15</v>
+      <c r="I346">
+        <v>1</v>
       </c>
       <c r="J346">
         <v>370</v>
@@ -15702,8 +15693,8 @@
       <c r="H347">
         <v>8.0136000000000003</v>
       </c>
-      <c r="I347" t="s">
-        <v>14</v>
+      <c r="I347">
+        <v>0</v>
       </c>
       <c r="J347">
         <v>352</v>
@@ -15746,8 +15737,8 @@
       <c r="H348">
         <v>8.0136000000000003</v>
       </c>
-      <c r="I348" t="s">
-        <v>14</v>
+      <c r="I348">
+        <v>0</v>
       </c>
       <c r="J348">
         <v>352</v>
@@ -15790,8 +15781,8 @@
       <c r="H349">
         <v>8.5352999999999994</v>
       </c>
-      <c r="I349" t="s">
-        <v>15</v>
+      <c r="I349">
+        <v>1</v>
       </c>
       <c r="J349">
         <v>351</v>
@@ -15834,8 +15825,8 @@
       <c r="H350">
         <v>8.3439999999999994</v>
       </c>
-      <c r="I350" t="s">
-        <v>15</v>
+      <c r="I350">
+        <v>1</v>
       </c>
       <c r="J350">
         <v>280</v>
@@ -15878,8 +15869,8 @@
       <c r="H351">
         <v>8.7920999999999996</v>
       </c>
-      <c r="I351" t="s">
-        <v>14</v>
+      <c r="I351">
+        <v>0</v>
       </c>
       <c r="J351">
         <v>335</v>
@@ -15922,8 +15913,8 @@
       <c r="H352">
         <v>8.7920999999999996</v>
       </c>
-      <c r="I352" t="s">
-        <v>14</v>
+      <c r="I352">
+        <v>0</v>
       </c>
       <c r="J352">
         <v>335</v>
@@ -15966,8 +15957,8 @@
       <c r="H353">
         <v>10.7103</v>
       </c>
-      <c r="I353" t="s">
-        <v>15</v>
+      <c r="I353">
+        <v>1</v>
       </c>
       <c r="J353">
         <v>411</v>
@@ -16010,8 +16001,8 @@
       <c r="H354">
         <v>10.7103</v>
       </c>
-      <c r="I354" t="s">
-        <v>15</v>
+      <c r="I354">
+        <v>1</v>
       </c>
       <c r="J354">
         <v>411</v>
@@ -16054,8 +16045,8 @@
       <c r="H355">
         <v>12.1265</v>
       </c>
-      <c r="I355" t="s">
-        <v>15</v>
+      <c r="I355">
+        <v>1</v>
       </c>
       <c r="J355">
         <v>187</v>
@@ -16098,8 +16089,8 @@
       <c r="H356">
         <v>10.585699999999999</v>
       </c>
-      <c r="I356" t="s">
-        <v>15</v>
+      <c r="I356">
+        <v>1</v>
       </c>
       <c r="J356">
         <v>334</v>
@@ -16142,8 +16133,8 @@
       <c r="H357">
         <v>10.585699999999999</v>
       </c>
-      <c r="I357" t="s">
-        <v>15</v>
+      <c r="I357">
+        <v>1</v>
       </c>
       <c r="J357">
         <v>334</v>
@@ -16186,8 +16177,8 @@
       <c r="H358">
         <v>2.1221999999999999</v>
       </c>
-      <c r="I358" t="s">
-        <v>16</v>
+      <c r="I358">
+        <v>2</v>
       </c>
       <c r="J358">
         <v>666</v>
@@ -16230,8 +16221,8 @@
       <c r="H359">
         <v>2.5051999999999999</v>
       </c>
-      <c r="I359" t="s">
-        <v>16</v>
+      <c r="I359">
+        <v>2</v>
       </c>
       <c r="J359">
         <v>666</v>
@@ -16274,8 +16265,8 @@
       <c r="H360">
         <v>2.7227000000000001</v>
       </c>
-      <c r="I360" t="s">
-        <v>16</v>
+      <c r="I360">
+        <v>2</v>
       </c>
       <c r="J360">
         <v>666</v>
@@ -16318,8 +16309,8 @@
       <c r="H361">
         <v>2.5091000000000001</v>
       </c>
-      <c r="I361" t="s">
-        <v>16</v>
+      <c r="I361">
+        <v>2</v>
       </c>
       <c r="J361">
         <v>666</v>
@@ -16362,8 +16353,8 @@
       <c r="H362">
         <v>2.5182000000000002</v>
       </c>
-      <c r="I362" t="s">
-        <v>16</v>
+      <c r="I362">
+        <v>2</v>
       </c>
       <c r="J362">
         <v>666</v>
@@ -16406,8 +16397,8 @@
       <c r="H363">
         <v>2.2955000000000001</v>
       </c>
-      <c r="I363" t="s">
-        <v>16</v>
+      <c r="I363">
+        <v>2</v>
       </c>
       <c r="J363">
         <v>666</v>
@@ -16450,8 +16441,8 @@
       <c r="H364">
         <v>2.1036000000000001</v>
       </c>
-      <c r="I364" t="s">
-        <v>16</v>
+      <c r="I364">
+        <v>2</v>
       </c>
       <c r="J364">
         <v>666</v>
@@ -16494,8 +16485,8 @@
       <c r="H365">
         <v>1.9047000000000001</v>
       </c>
-      <c r="I365" t="s">
-        <v>16</v>
+      <c r="I365">
+        <v>2</v>
       </c>
       <c r="J365">
         <v>666</v>
@@ -16538,8 +16529,8 @@
       <c r="H366">
         <v>1.9047000000000001</v>
       </c>
-      <c r="I366" t="s">
-        <v>16</v>
+      <c r="I366">
+        <v>2</v>
       </c>
       <c r="J366">
         <v>666</v>
@@ -16582,8 +16573,8 @@
       <c r="H367">
         <v>1.6132</v>
       </c>
-      <c r="I367" t="s">
-        <v>16</v>
+      <c r="I367">
+        <v>2</v>
       </c>
       <c r="J367">
         <v>666</v>
@@ -16626,8 +16617,8 @@
       <c r="H368">
         <v>1.7523</v>
       </c>
-      <c r="I368" t="s">
-        <v>16</v>
+      <c r="I368">
+        <v>2</v>
       </c>
       <c r="J368">
         <v>666</v>
@@ -16670,8 +16661,8 @@
       <c r="H369">
         <v>1.5105999999999999</v>
       </c>
-      <c r="I369" t="s">
-        <v>16</v>
+      <c r="I369">
+        <v>2</v>
       </c>
       <c r="J369">
         <v>666</v>
@@ -16714,8 +16705,8 @@
       <c r="H370">
         <v>1.3325</v>
       </c>
-      <c r="I370" t="s">
-        <v>16</v>
+      <c r="I370">
+        <v>2</v>
       </c>
       <c r="J370">
         <v>666</v>
@@ -16758,8 +16749,8 @@
       <c r="H371">
         <v>1.3567</v>
       </c>
-      <c r="I371" t="s">
-        <v>16</v>
+      <c r="I371">
+        <v>2</v>
       </c>
       <c r="J371">
         <v>666</v>
@@ -16802,8 +16793,8 @@
       <c r="H372">
         <v>1.2023999999999999</v>
       </c>
-      <c r="I372" t="s">
-        <v>16</v>
+      <c r="I372">
+        <v>2</v>
       </c>
       <c r="J372">
         <v>666</v>
@@ -16846,8 +16837,8 @@
       <c r="H373">
         <v>1.1691</v>
       </c>
-      <c r="I373" t="s">
-        <v>16</v>
+      <c r="I373">
+        <v>2</v>
       </c>
       <c r="J373">
         <v>666</v>
@@ -16890,8 +16881,8 @@
       <c r="H374">
         <v>1.1295999999999999</v>
       </c>
-      <c r="I374" t="s">
-        <v>16</v>
+      <c r="I374">
+        <v>2</v>
       </c>
       <c r="J374">
         <v>666</v>
@@ -16934,8 +16925,8 @@
       <c r="H375">
         <v>1.1741999999999999</v>
       </c>
-      <c r="I375" t="s">
-        <v>16</v>
+      <c r="I375">
+        <v>2</v>
       </c>
       <c r="J375">
         <v>666</v>
@@ -16978,8 +16969,8 @@
       <c r="H376">
         <v>1.137</v>
       </c>
-      <c r="I376" t="s">
-        <v>16</v>
+      <c r="I376">
+        <v>2</v>
       </c>
       <c r="J376">
         <v>666</v>
@@ -17022,8 +17013,8 @@
       <c r="H377">
         <v>1.3163</v>
       </c>
-      <c r="I377" t="s">
-        <v>16</v>
+      <c r="I377">
+        <v>2</v>
       </c>
       <c r="J377">
         <v>666</v>
@@ -17066,8 +17057,8 @@
       <c r="H378">
         <v>1.3449</v>
       </c>
-      <c r="I378" t="s">
-        <v>16</v>
+      <c r="I378">
+        <v>2</v>
       </c>
       <c r="J378">
         <v>666</v>
@@ -17110,8 +17101,8 @@
       <c r="H379">
         <v>1.3580000000000001</v>
       </c>
-      <c r="I379" t="s">
-        <v>16</v>
+      <c r="I379">
+        <v>2</v>
       </c>
       <c r="J379">
         <v>666</v>
@@ -17154,8 +17145,8 @@
       <c r="H380">
         <v>1.3861000000000001</v>
       </c>
-      <c r="I380" t="s">
-        <v>16</v>
+      <c r="I380">
+        <v>2</v>
       </c>
       <c r="J380">
         <v>666</v>
@@ -17198,8 +17189,8 @@
       <c r="H381">
         <v>1.3861000000000001</v>
       </c>
-      <c r="I381" t="s">
-        <v>16</v>
+      <c r="I381">
+        <v>2</v>
       </c>
       <c r="J381">
         <v>666</v>
@@ -17242,8 +17233,8 @@
       <c r="H382">
         <v>1.4165000000000001</v>
       </c>
-      <c r="I382" t="s">
-        <v>16</v>
+      <c r="I382">
+        <v>2</v>
       </c>
       <c r="J382">
         <v>666</v>
@@ -17286,8 +17277,8 @@
       <c r="H383">
         <v>1.5192000000000001</v>
       </c>
-      <c r="I383" t="s">
-        <v>16</v>
+      <c r="I383">
+        <v>2</v>
       </c>
       <c r="J383">
         <v>666</v>
@@ -17330,8 +17321,8 @@
       <c r="H384">
         <v>1.5804</v>
       </c>
-      <c r="I384" t="s">
-        <v>16</v>
+      <c r="I384">
+        <v>2</v>
       </c>
       <c r="J384">
         <v>666</v>
@@ -17374,8 +17365,8 @@
       <c r="H385">
         <v>1.5330999999999999</v>
       </c>
-      <c r="I385" t="s">
-        <v>16</v>
+      <c r="I385">
+        <v>2</v>
       </c>
       <c r="J385">
         <v>666</v>
@@ -17418,8 +17409,8 @@
       <c r="H386">
         <v>1.4395</v>
       </c>
-      <c r="I386" t="s">
-        <v>16</v>
+      <c r="I386">
+        <v>2</v>
       </c>
       <c r="J386">
         <v>666</v>
@@ -17462,8 +17453,8 @@
       <c r="H387">
         <v>1.4260999999999999</v>
       </c>
-      <c r="I387" t="s">
-        <v>16</v>
+      <c r="I387">
+        <v>2</v>
       </c>
       <c r="J387">
         <v>666</v>
@@ -17506,8 +17497,8 @@
       <c r="H388">
         <v>1.4672000000000001</v>
       </c>
-      <c r="I388" t="s">
-        <v>16</v>
+      <c r="I388">
+        <v>2</v>
       </c>
       <c r="J388">
         <v>666</v>
@@ -17550,8 +17541,8 @@
       <c r="H389">
         <v>1.5184</v>
       </c>
-      <c r="I389" t="s">
-        <v>16</v>
+      <c r="I389">
+        <v>2</v>
       </c>
       <c r="J389">
         <v>666</v>
@@ -17594,8 +17585,8 @@
       <c r="H390">
         <v>1.5894999999999999</v>
       </c>
-      <c r="I390" t="s">
-        <v>16</v>
+      <c r="I390">
+        <v>2</v>
       </c>
       <c r="J390">
         <v>666</v>
@@ -17638,8 +17629,8 @@
       <c r="H391">
         <v>1.7281</v>
       </c>
-      <c r="I391" t="s">
-        <v>16</v>
+      <c r="I391">
+        <v>2</v>
       </c>
       <c r="J391">
         <v>666</v>
@@ -17682,8 +17673,8 @@
       <c r="H392">
         <v>1.9265000000000001</v>
       </c>
-      <c r="I392" t="s">
-        <v>16</v>
+      <c r="I392">
+        <v>2</v>
       </c>
       <c r="J392">
         <v>666</v>
@@ -17726,8 +17717,8 @@
       <c r="H393">
         <v>2.1678000000000002</v>
       </c>
-      <c r="I393" t="s">
-        <v>16</v>
+      <c r="I393">
+        <v>2</v>
       </c>
       <c r="J393">
         <v>666</v>
@@ -17770,8 +17761,8 @@
       <c r="H394">
         <v>1.77</v>
       </c>
-      <c r="I394" t="s">
-        <v>16</v>
+      <c r="I394">
+        <v>2</v>
       </c>
       <c r="J394">
         <v>666</v>
@@ -17814,8 +17805,8 @@
       <c r="H395">
         <v>1.7911999999999999</v>
       </c>
-      <c r="I395" t="s">
-        <v>16</v>
+      <c r="I395">
+        <v>2</v>
       </c>
       <c r="J395">
         <v>666</v>
@@ -17858,8 +17849,8 @@
       <c r="H396">
         <v>1.7821</v>
       </c>
-      <c r="I396" t="s">
-        <v>16</v>
+      <c r="I396">
+        <v>2</v>
       </c>
       <c r="J396">
         <v>666</v>
@@ -17902,8 +17893,8 @@
       <c r="H397">
         <v>1.7257</v>
       </c>
-      <c r="I397" t="s">
-        <v>16</v>
+      <c r="I397">
+        <v>2</v>
       </c>
       <c r="J397">
         <v>666</v>
@@ -17946,8 +17937,8 @@
       <c r="H398">
         <v>1.6768000000000001</v>
       </c>
-      <c r="I398" t="s">
-        <v>16</v>
+      <c r="I398">
+        <v>2</v>
       </c>
       <c r="J398">
         <v>666</v>
@@ -17990,8 +17981,8 @@
       <c r="H399">
         <v>1.6334</v>
       </c>
-      <c r="I399" t="s">
-        <v>16</v>
+      <c r="I399">
+        <v>2</v>
       </c>
       <c r="J399">
         <v>666</v>
@@ -18034,8 +18025,8 @@
       <c r="H400">
         <v>1.4896</v>
       </c>
-      <c r="I400" t="s">
-        <v>16</v>
+      <c r="I400">
+        <v>2</v>
       </c>
       <c r="J400">
         <v>666</v>
@@ -18078,8 +18069,8 @@
       <c r="H401">
         <v>1.5004</v>
       </c>
-      <c r="I401" t="s">
-        <v>16</v>
+      <c r="I401">
+        <v>2</v>
       </c>
       <c r="J401">
         <v>666</v>
@@ -18122,8 +18113,8 @@
       <c r="H402">
         <v>1.5888</v>
       </c>
-      <c r="I402" t="s">
-        <v>16</v>
+      <c r="I402">
+        <v>2</v>
       </c>
       <c r="J402">
         <v>666</v>
@@ -18166,8 +18157,8 @@
       <c r="H403">
         <v>1.5741000000000001</v>
       </c>
-      <c r="I403" t="s">
-        <v>16</v>
+      <c r="I403">
+        <v>2</v>
       </c>
       <c r="J403">
         <v>666</v>
@@ -18210,8 +18201,8 @@
       <c r="H404">
         <v>1.639</v>
       </c>
-      <c r="I404" t="s">
-        <v>16</v>
+      <c r="I404">
+        <v>2</v>
       </c>
       <c r="J404">
         <v>666</v>
@@ -18254,8 +18245,8 @@
       <c r="H405">
         <v>1.7028000000000001</v>
       </c>
-      <c r="I405" t="s">
-        <v>16</v>
+      <c r="I405">
+        <v>2</v>
       </c>
       <c r="J405">
         <v>666</v>
@@ -18298,8 +18289,8 @@
       <c r="H406">
         <v>1.6073999999999999</v>
       </c>
-      <c r="I406" t="s">
-        <v>16</v>
+      <c r="I406">
+        <v>2</v>
       </c>
       <c r="J406">
         <v>666</v>
@@ -18342,8 +18333,8 @@
       <c r="H407">
         <v>1.4254</v>
       </c>
-      <c r="I407" t="s">
-        <v>16</v>
+      <c r="I407">
+        <v>2</v>
       </c>
       <c r="J407">
         <v>666</v>
@@ -18386,8 +18377,8 @@
       <c r="H408">
         <v>1.1780999999999999</v>
       </c>
-      <c r="I408" t="s">
-        <v>16</v>
+      <c r="I408">
+        <v>2</v>
       </c>
       <c r="J408">
         <v>666</v>
@@ -18430,8 +18421,8 @@
       <c r="H409">
         <v>1.2851999999999999</v>
       </c>
-      <c r="I409" t="s">
-        <v>16</v>
+      <c r="I409">
+        <v>2</v>
       </c>
       <c r="J409">
         <v>666</v>
@@ -18474,8 +18465,8 @@
       <c r="H410">
         <v>1.4547000000000001</v>
       </c>
-      <c r="I410" t="s">
-        <v>16</v>
+      <c r="I410">
+        <v>2</v>
       </c>
       <c r="J410">
         <v>666</v>
@@ -18518,8 +18509,8 @@
       <c r="H411">
         <v>1.4655</v>
       </c>
-      <c r="I411" t="s">
-        <v>16</v>
+      <c r="I411">
+        <v>2</v>
       </c>
       <c r="J411">
         <v>666</v>
@@ -18562,8 +18553,8 @@
       <c r="H412">
         <v>1.413</v>
       </c>
-      <c r="I412" t="s">
-        <v>16</v>
+      <c r="I412">
+        <v>2</v>
       </c>
       <c r="J412">
         <v>666</v>
@@ -18606,8 +18597,8 @@
       <c r="H413">
         <v>1.5275000000000001</v>
       </c>
-      <c r="I413" t="s">
-        <v>16</v>
+      <c r="I413">
+        <v>2</v>
       </c>
       <c r="J413">
         <v>666</v>
@@ -18650,8 +18641,8 @@
       <c r="H414">
         <v>1.5539000000000001</v>
       </c>
-      <c r="I414" t="s">
-        <v>16</v>
+      <c r="I414">
+        <v>2</v>
       </c>
       <c r="J414">
         <v>666</v>
@@ -18694,8 +18685,8 @@
       <c r="H415">
         <v>1.5893999999999999</v>
       </c>
-      <c r="I415" t="s">
-        <v>16</v>
+      <c r="I415">
+        <v>2</v>
       </c>
       <c r="J415">
         <v>666</v>
@@ -18738,8 +18729,8 @@
       <c r="H416">
         <v>1.6581999999999999</v>
       </c>
-      <c r="I416" t="s">
-        <v>16</v>
+      <c r="I416">
+        <v>2</v>
       </c>
       <c r="J416">
         <v>666</v>
@@ -18782,8 +18773,8 @@
       <c r="H417">
         <v>1.8347</v>
       </c>
-      <c r="I417" t="s">
-        <v>16</v>
+      <c r="I417">
+        <v>2</v>
       </c>
       <c r="J417">
         <v>666</v>
@@ -18826,8 +18817,8 @@
       <c r="H418">
         <v>1.8194999999999999</v>
       </c>
-      <c r="I418" t="s">
-        <v>16</v>
+      <c r="I418">
+        <v>2</v>
       </c>
       <c r="J418">
         <v>666</v>
@@ -18870,8 +18861,8 @@
       <c r="H419">
         <v>1.6475</v>
       </c>
-      <c r="I419" t="s">
-        <v>16</v>
+      <c r="I419">
+        <v>2</v>
       </c>
       <c r="J419">
         <v>666</v>
@@ -18914,8 +18905,8 @@
       <c r="H420">
         <v>1.8026</v>
       </c>
-      <c r="I420" t="s">
-        <v>16</v>
+      <c r="I420">
+        <v>2</v>
       </c>
       <c r="J420">
         <v>666</v>
@@ -18958,8 +18949,8 @@
       <c r="H421">
         <v>1.794</v>
       </c>
-      <c r="I421" t="s">
-        <v>16</v>
+      <c r="I421">
+        <v>2</v>
       </c>
       <c r="J421">
         <v>666</v>
@@ -19002,8 +18993,8 @@
       <c r="H422">
         <v>1.8589</v>
       </c>
-      <c r="I422" t="s">
-        <v>16</v>
+      <c r="I422">
+        <v>2</v>
       </c>
       <c r="J422">
         <v>666</v>
@@ -19046,8 +19037,8 @@
       <c r="H423">
         <v>1.8746</v>
       </c>
-      <c r="I423" t="s">
-        <v>16</v>
+      <c r="I423">
+        <v>2</v>
       </c>
       <c r="J423">
         <v>666</v>
@@ -19090,8 +19081,8 @@
       <c r="H424">
         <v>1.9512</v>
       </c>
-      <c r="I424" t="s">
-        <v>16</v>
+      <c r="I424">
+        <v>2</v>
       </c>
       <c r="J424">
         <v>666</v>
@@ -19134,8 +19125,8 @@
       <c r="H425">
         <v>2.0217999999999998</v>
       </c>
-      <c r="I425" t="s">
-        <v>16</v>
+      <c r="I425">
+        <v>2</v>
       </c>
       <c r="J425">
         <v>666</v>
@@ -19178,8 +19169,8 @@
       <c r="H426">
         <v>2.0634999999999999</v>
       </c>
-      <c r="I426" t="s">
-        <v>16</v>
+      <c r="I426">
+        <v>2</v>
       </c>
       <c r="J426">
         <v>666</v>
@@ -19222,8 +19213,8 @@
       <c r="H427">
         <v>1.9096</v>
       </c>
-      <c r="I427" t="s">
-        <v>16</v>
+      <c r="I427">
+        <v>2</v>
       </c>
       <c r="J427">
         <v>666</v>
@@ -19266,8 +19257,8 @@
       <c r="H428">
         <v>1.9976</v>
       </c>
-      <c r="I428" t="s">
-        <v>16</v>
+      <c r="I428">
+        <v>2</v>
       </c>
       <c r="J428">
         <v>666</v>
@@ -19310,8 +19301,8 @@
       <c r="H429">
         <v>1.8629</v>
       </c>
-      <c r="I429" t="s">
-        <v>16</v>
+      <c r="I429">
+        <v>2</v>
       </c>
       <c r="J429">
         <v>666</v>
@@ -19354,8 +19345,8 @@
       <c r="H430">
         <v>1.9356</v>
       </c>
-      <c r="I430" t="s">
-        <v>16</v>
+      <c r="I430">
+        <v>2</v>
       </c>
       <c r="J430">
         <v>666</v>
@@ -19398,8 +19389,8 @@
       <c r="H431">
         <v>1.9681999999999999</v>
       </c>
-      <c r="I431" t="s">
-        <v>16</v>
+      <c r="I431">
+        <v>2</v>
       </c>
       <c r="J431">
         <v>666</v>
@@ -19442,8 +19433,8 @@
       <c r="H432">
         <v>2.0527000000000002</v>
       </c>
-      <c r="I432" t="s">
-        <v>16</v>
+      <c r="I432">
+        <v>2</v>
       </c>
       <c r="J432">
         <v>666</v>
@@ -19486,8 +19477,8 @@
       <c r="H433">
         <v>2.0882000000000001</v>
       </c>
-      <c r="I433" t="s">
-        <v>16</v>
+      <c r="I433">
+        <v>2</v>
       </c>
       <c r="J433">
         <v>666</v>
@@ -19530,8 +19521,8 @@
       <c r="H434">
         <v>2.2004000000000001</v>
       </c>
-      <c r="I434" t="s">
-        <v>16</v>
+      <c r="I434">
+        <v>2</v>
       </c>
       <c r="J434">
         <v>666</v>
@@ -19574,8 +19565,8 @@
       <c r="H435">
         <v>2.3157999999999999</v>
       </c>
-      <c r="I435" t="s">
-        <v>16</v>
+      <c r="I435">
+        <v>2</v>
       </c>
       <c r="J435">
         <v>666</v>
@@ -19618,8 +19609,8 @@
       <c r="H436">
         <v>2.2222</v>
       </c>
-      <c r="I436" t="s">
-        <v>16</v>
+      <c r="I436">
+        <v>2</v>
       </c>
       <c r="J436">
         <v>666</v>
@@ -19662,8 +19653,8 @@
       <c r="H437">
         <v>2.1246999999999998</v>
       </c>
-      <c r="I437" t="s">
-        <v>16</v>
+      <c r="I437">
+        <v>2</v>
       </c>
       <c r="J437">
         <v>666</v>
@@ -19706,8 +19697,8 @@
       <c r="H438">
         <v>2.0026000000000002</v>
       </c>
-      <c r="I438" t="s">
-        <v>16</v>
+      <c r="I438">
+        <v>2</v>
       </c>
       <c r="J438">
         <v>666</v>
@@ -19750,8 +19741,8 @@
       <c r="H439">
         <v>1.9141999999999999</v>
       </c>
-      <c r="I439" t="s">
-        <v>16</v>
+      <c r="I439">
+        <v>2</v>
       </c>
       <c r="J439">
         <v>666</v>
@@ -19794,8 +19785,8 @@
       <c r="H440">
         <v>1.8206</v>
       </c>
-      <c r="I440" t="s">
-        <v>16</v>
+      <c r="I440">
+        <v>2</v>
       </c>
       <c r="J440">
         <v>666</v>
@@ -19838,8 +19829,8 @@
       <c r="H441">
         <v>1.8171999999999999</v>
       </c>
-      <c r="I441" t="s">
-        <v>16</v>
+      <c r="I441">
+        <v>2</v>
       </c>
       <c r="J441">
         <v>666</v>
@@ -19882,8 +19873,8 @@
       <c r="H442">
         <v>1.8662000000000001</v>
       </c>
-      <c r="I442" t="s">
-        <v>16</v>
+      <c r="I442">
+        <v>2</v>
       </c>
       <c r="J442">
         <v>666</v>
@@ -19926,8 +19917,8 @@
       <c r="H443">
         <v>2.0651000000000002</v>
       </c>
-      <c r="I443" t="s">
-        <v>16</v>
+      <c r="I443">
+        <v>2</v>
       </c>
       <c r="J443">
         <v>666</v>
@@ -19970,8 +19961,8 @@
       <c r="H444">
         <v>2.0047999999999999</v>
       </c>
-      <c r="I444" t="s">
-        <v>16</v>
+      <c r="I444">
+        <v>2</v>
       </c>
       <c r="J444">
         <v>666</v>
@@ -20014,8 +20005,8 @@
       <c r="H445">
         <v>1.9783999999999999</v>
       </c>
-      <c r="I445" t="s">
-        <v>16</v>
+      <c r="I445">
+        <v>2</v>
       </c>
       <c r="J445">
         <v>666</v>
@@ -20058,8 +20049,8 @@
       <c r="H446">
         <v>1.8956</v>
       </c>
-      <c r="I446" t="s">
-        <v>16</v>
+      <c r="I446">
+        <v>2</v>
       </c>
       <c r="J446">
         <v>666</v>
@@ -20102,8 +20093,8 @@
       <c r="H447">
         <v>1.9879</v>
       </c>
-      <c r="I447" t="s">
-        <v>16</v>
+      <c r="I447">
+        <v>2</v>
       </c>
       <c r="J447">
         <v>666</v>
@@ -20146,8 +20137,8 @@
       <c r="H448">
         <v>2.0720000000000001</v>
       </c>
-      <c r="I448" t="s">
-        <v>16</v>
+      <c r="I448">
+        <v>2</v>
       </c>
       <c r="J448">
         <v>666</v>
@@ -20190,8 +20181,8 @@
       <c r="H449">
         <v>2.198</v>
       </c>
-      <c r="I449" t="s">
-        <v>16</v>
+      <c r="I449">
+        <v>2</v>
       </c>
       <c r="J449">
         <v>666</v>
@@ -20234,8 +20225,8 @@
       <c r="H450">
         <v>2.2616000000000001</v>
       </c>
-      <c r="I450" t="s">
-        <v>16</v>
+      <c r="I450">
+        <v>2</v>
       </c>
       <c r="J450">
         <v>666</v>
@@ -20278,8 +20269,8 @@
       <c r="H451">
         <v>2.1850000000000001</v>
       </c>
-      <c r="I451" t="s">
-        <v>16</v>
+      <c r="I451">
+        <v>2</v>
       </c>
       <c r="J451">
         <v>666</v>
@@ -20322,8 +20313,8 @@
       <c r="H452">
         <v>2.3235999999999999</v>
       </c>
-      <c r="I452" t="s">
-        <v>16</v>
+      <c r="I452">
+        <v>2</v>
       </c>
       <c r="J452">
         <v>666</v>
@@ -20366,8 +20357,8 @@
       <c r="H453">
         <v>2.3552</v>
       </c>
-      <c r="I453" t="s">
-        <v>16</v>
+      <c r="I453">
+        <v>2</v>
       </c>
       <c r="J453">
         <v>666</v>
@@ -20410,8 +20401,8 @@
       <c r="H454">
         <v>2.3681999999999999</v>
       </c>
-      <c r="I454" t="s">
-        <v>16</v>
+      <c r="I454">
+        <v>2</v>
       </c>
       <c r="J454">
         <v>666</v>
@@ -20454,8 +20445,8 @@
       <c r="H455">
         <v>2.4527000000000001</v>
       </c>
-      <c r="I455" t="s">
-        <v>16</v>
+      <c r="I455">
+        <v>2</v>
       </c>
       <c r="J455">
         <v>666</v>
@@ -20498,8 +20489,8 @@
       <c r="H456">
         <v>2.4961000000000002</v>
       </c>
-      <c r="I456" t="s">
-        <v>16</v>
+      <c r="I456">
+        <v>2</v>
       </c>
       <c r="J456">
         <v>666</v>
@@ -20542,8 +20533,8 @@
       <c r="H457">
         <v>2.4358</v>
       </c>
-      <c r="I457" t="s">
-        <v>16</v>
+      <c r="I457">
+        <v>2</v>
       </c>
       <c r="J457">
         <v>666</v>
@@ -20586,8 +20577,8 @@
       <c r="H458">
         <v>2.5806</v>
       </c>
-      <c r="I458" t="s">
-        <v>16</v>
+      <c r="I458">
+        <v>2</v>
       </c>
       <c r="J458">
         <v>666</v>
@@ -20630,8 +20621,8 @@
       <c r="H459">
         <v>2.7791999999999999</v>
       </c>
-      <c r="I459" t="s">
-        <v>16</v>
+      <c r="I459">
+        <v>2</v>
       </c>
       <c r="J459">
         <v>666</v>
@@ -20674,8 +20665,8 @@
       <c r="H460">
         <v>2.7831000000000001</v>
       </c>
-      <c r="I460" t="s">
-        <v>16</v>
+      <c r="I460">
+        <v>2</v>
       </c>
       <c r="J460">
         <v>666</v>
@@ -20718,8 +20709,8 @@
       <c r="H461">
         <v>2.7174999999999998</v>
       </c>
-      <c r="I461" t="s">
-        <v>16</v>
+      <c r="I461">
+        <v>2</v>
       </c>
       <c r="J461">
         <v>666</v>
@@ -20762,8 +20753,8 @@
       <c r="H462">
         <v>2.5975000000000001</v>
       </c>
-      <c r="I462" t="s">
-        <v>16</v>
+      <c r="I462">
+        <v>2</v>
       </c>
       <c r="J462">
         <v>666</v>
@@ -20806,8 +20797,8 @@
       <c r="H463">
         <v>2.5670999999999999</v>
       </c>
-      <c r="I463" t="s">
-        <v>16</v>
+      <c r="I463">
+        <v>2</v>
       </c>
       <c r="J463">
         <v>666</v>
@@ -20850,8 +20841,8 @@
       <c r="H464">
         <v>2.7343999999999999</v>
       </c>
-      <c r="I464" t="s">
-        <v>16</v>
+      <c r="I464">
+        <v>2</v>
       </c>
       <c r="J464">
         <v>666</v>
@@ -20894,8 +20885,8 @@
       <c r="H465">
         <v>2.8016000000000001</v>
       </c>
-      <c r="I465" t="s">
-        <v>16</v>
+      <c r="I465">
+        <v>2</v>
       </c>
       <c r="J465">
         <v>666</v>
@@ -20938,8 +20929,8 @@
       <c r="H466">
         <v>2.9634</v>
       </c>
-      <c r="I466" t="s">
-        <v>16</v>
+      <c r="I466">
+        <v>2</v>
       </c>
       <c r="J466">
         <v>666</v>
@@ -20982,8 +20973,8 @@
       <c r="H467">
         <v>3.0665</v>
       </c>
-      <c r="I467" t="s">
-        <v>16</v>
+      <c r="I467">
+        <v>2</v>
       </c>
       <c r="J467">
         <v>666</v>
@@ -21026,8 +21017,8 @@
       <c r="H468">
         <v>2.8715000000000002</v>
       </c>
-      <c r="I468" t="s">
-        <v>16</v>
+      <c r="I468">
+        <v>2</v>
       </c>
       <c r="J468">
         <v>666</v>
@@ -21070,8 +21061,8 @@
       <c r="H469">
         <v>2.5402999999999998</v>
       </c>
-      <c r="I469" t="s">
-        <v>16</v>
+      <c r="I469">
+        <v>2</v>
       </c>
       <c r="J469">
         <v>666</v>
@@ -21114,8 +21105,8 @@
       <c r="H470">
         <v>2.9083999999999999</v>
       </c>
-      <c r="I470" t="s">
-        <v>16</v>
+      <c r="I470">
+        <v>2</v>
       </c>
       <c r="J470">
         <v>666</v>
@@ -21158,8 +21149,8 @@
       <c r="H471">
         <v>2.8237000000000001</v>
       </c>
-      <c r="I471" t="s">
-        <v>16</v>
+      <c r="I471">
+        <v>2</v>
       </c>
       <c r="J471">
         <v>666</v>
@@ -21202,8 +21193,8 @@
       <c r="H472">
         <v>3.0333999999999999</v>
       </c>
-      <c r="I472" t="s">
-        <v>16</v>
+      <c r="I472">
+        <v>2</v>
       </c>
       <c r="J472">
         <v>666</v>
@@ -21246,8 +21237,8 @@
       <c r="H473">
         <v>3.0992999999999999</v>
       </c>
-      <c r="I473" t="s">
-        <v>16</v>
+      <c r="I473">
+        <v>2</v>
       </c>
       <c r="J473">
         <v>666</v>
@@ -21290,8 +21281,8 @@
       <c r="H474">
         <v>2.8965000000000001</v>
       </c>
-      <c r="I474" t="s">
-        <v>16</v>
+      <c r="I474">
+        <v>2</v>
       </c>
       <c r="J474">
         <v>666</v>
@@ -21334,8 +21325,8 @@
       <c r="H475">
         <v>2.5329000000000002</v>
       </c>
-      <c r="I475" t="s">
-        <v>16</v>
+      <c r="I475">
+        <v>2</v>
       </c>
       <c r="J475">
         <v>666</v>
@@ -21378,8 +21369,8 @@
       <c r="H476">
         <v>2.4298000000000002</v>
       </c>
-      <c r="I476" t="s">
-        <v>16</v>
+      <c r="I476">
+        <v>2</v>
       </c>
       <c r="J476">
         <v>666</v>
@@ -21422,8 +21413,8 @@
       <c r="H477">
         <v>2.206</v>
       </c>
-      <c r="I477" t="s">
-        <v>16</v>
+      <c r="I477">
+        <v>2</v>
       </c>
       <c r="J477">
         <v>666</v>
@@ -21466,8 +21457,8 @@
       <c r="H478">
         <v>2.3052999999999999</v>
       </c>
-      <c r="I478" t="s">
-        <v>16</v>
+      <c r="I478">
+        <v>2</v>
       </c>
       <c r="J478">
         <v>666</v>
@@ -21510,8 +21501,8 @@
       <c r="H479">
         <v>2.1006999999999998</v>
       </c>
-      <c r="I479" t="s">
-        <v>16</v>
+      <c r="I479">
+        <v>2</v>
       </c>
       <c r="J479">
         <v>666</v>
@@ -21554,8 +21545,8 @@
       <c r="H480">
         <v>2.1705000000000001</v>
       </c>
-      <c r="I480" t="s">
-        <v>16</v>
+      <c r="I480">
+        <v>2</v>
       </c>
       <c r="J480">
         <v>666</v>
@@ -21598,8 +21589,8 @@
       <c r="H481">
         <v>1.9512</v>
       </c>
-      <c r="I481" t="s">
-        <v>16</v>
+      <c r="I481">
+        <v>2</v>
       </c>
       <c r="J481">
         <v>666</v>
@@ -21642,8 +21633,8 @@
       <c r="H482">
         <v>3.4241999999999999</v>
       </c>
-      <c r="I482" t="s">
-        <v>16</v>
+      <c r="I482">
+        <v>2</v>
       </c>
       <c r="J482">
         <v>666</v>
@@ -21686,8 +21677,8 @@
       <c r="H483">
         <v>3.3317000000000001</v>
       </c>
-      <c r="I483" t="s">
-        <v>16</v>
+      <c r="I483">
+        <v>2</v>
       </c>
       <c r="J483">
         <v>666</v>
@@ -21730,8 +21721,8 @@
       <c r="H484">
         <v>3.4106000000000001</v>
       </c>
-      <c r="I484" t="s">
-        <v>16</v>
+      <c r="I484">
+        <v>2</v>
       </c>
       <c r="J484">
         <v>666</v>
@@ -21774,8 +21765,8 @@
       <c r="H485">
         <v>4.0983000000000001</v>
       </c>
-      <c r="I485" t="s">
-        <v>16</v>
+      <c r="I485">
+        <v>2</v>
       </c>
       <c r="J485">
         <v>666</v>
@@ -21818,8 +21809,8 @@
       <c r="H486">
         <v>3.7240000000000002</v>
       </c>
-      <c r="I486" t="s">
-        <v>16</v>
+      <c r="I486">
+        <v>2</v>
       </c>
       <c r="J486">
         <v>666</v>
@@ -21862,8 +21853,8 @@
       <c r="H487">
         <v>3.9916999999999998</v>
       </c>
-      <c r="I487" t="s">
-        <v>16</v>
+      <c r="I487">
+        <v>2</v>
       </c>
       <c r="J487">
         <v>666</v>
@@ -21906,8 +21897,8 @@
       <c r="H488">
         <v>3.5459000000000001</v>
       </c>
-      <c r="I488" t="s">
-        <v>16</v>
+      <c r="I488">
+        <v>2</v>
       </c>
       <c r="J488">
         <v>666</v>
@@ -21950,8 +21941,8 @@
       <c r="H489">
         <v>3.1522999999999999</v>
       </c>
-      <c r="I489" t="s">
-        <v>16</v>
+      <c r="I489">
+        <v>2</v>
       </c>
       <c r="J489">
         <v>666</v>
@@ -21994,8 +21985,8 @@
       <c r="H490">
         <v>1.8209</v>
       </c>
-      <c r="I490" t="s">
-        <v>15</v>
+      <c r="I490">
+        <v>1</v>
       </c>
       <c r="J490">
         <v>711</v>
@@ -22038,8 +22029,8 @@
       <c r="H491">
         <v>1.7554000000000001</v>
       </c>
-      <c r="I491" t="s">
-        <v>15</v>
+      <c r="I491">
+        <v>1</v>
       </c>
       <c r="J491">
         <v>711</v>
@@ -22082,8 +22073,8 @@
       <c r="H492">
         <v>1.8226</v>
       </c>
-      <c r="I492" t="s">
-        <v>15</v>
+      <c r="I492">
+        <v>1</v>
       </c>
       <c r="J492">
         <v>711</v>
@@ -22126,8 +22117,8 @@
       <c r="H493">
         <v>1.8681000000000001</v>
       </c>
-      <c r="I493" t="s">
-        <v>15</v>
+      <c r="I493">
+        <v>1</v>
       </c>
       <c r="J493">
         <v>711</v>
@@ -22170,8 +22161,8 @@
       <c r="H494">
         <v>2.1099000000000001</v>
       </c>
-      <c r="I494" t="s">
-        <v>15</v>
+      <c r="I494">
+        <v>1</v>
       </c>
       <c r="J494">
         <v>711</v>
@@ -22214,8 +22205,8 @@
       <c r="H495">
         <v>2.3816999999999999</v>
       </c>
-      <c r="I495" t="s">
-        <v>15</v>
+      <c r="I495">
+        <v>1</v>
       </c>
       <c r="J495">
         <v>391</v>
@@ -22258,8 +22249,8 @@
       <c r="H496">
         <v>2.3816999999999999</v>
       </c>
-      <c r="I496" t="s">
-        <v>15</v>
+      <c r="I496">
+        <v>1</v>
       </c>
       <c r="J496">
         <v>391</v>
@@ -22302,8 +22293,8 @@
       <c r="H497">
         <v>2.7986</v>
       </c>
-      <c r="I497" t="s">
-        <v>15</v>
+      <c r="I497">
+        <v>1</v>
       </c>
       <c r="J497">
         <v>391</v>
@@ -22346,8 +22337,8 @@
       <c r="H498">
         <v>2.7986</v>
       </c>
-      <c r="I498" t="s">
-        <v>15</v>
+      <c r="I498">
+        <v>1</v>
       </c>
       <c r="J498">
         <v>391</v>
@@ -22390,8 +22381,8 @@
       <c r="H499">
         <v>2.8927</v>
       </c>
-      <c r="I499" t="s">
-        <v>15</v>
+      <c r="I499">
+        <v>1</v>
       </c>
       <c r="J499">
         <v>391</v>
@@ -22434,8 +22425,8 @@
       <c r="H500">
         <v>2.4091</v>
       </c>
-      <c r="I500" t="s">
-        <v>15</v>
+      <c r="I500">
+        <v>1</v>
       </c>
       <c r="J500">
         <v>391</v>
@@ -22478,8 +22469,8 @@
       <c r="H501">
         <v>2.3999000000000001</v>
       </c>
-      <c r="I501" t="s">
-        <v>15</v>
+      <c r="I501">
+        <v>1</v>
       </c>
       <c r="J501">
         <v>391</v>
@@ -22522,8 +22513,8 @@
       <c r="H502">
         <v>2.4982000000000002</v>
       </c>
-      <c r="I502" t="s">
-        <v>15</v>
+      <c r="I502">
+        <v>1</v>
       </c>
       <c r="J502">
         <v>391</v>
@@ -22566,8 +22557,8 @@
       <c r="H503">
         <v>2.4786000000000001</v>
       </c>
-      <c r="I503" t="s">
-        <v>14</v>
+      <c r="I503">
+        <v>0</v>
       </c>
       <c r="J503">
         <v>273</v>
@@ -22610,8 +22601,8 @@
       <c r="H504">
         <v>2.2875000000000001</v>
       </c>
-      <c r="I504" t="s">
-        <v>14</v>
+      <c r="I504">
+        <v>0</v>
       </c>
       <c r="J504">
         <v>273</v>
@@ -22654,8 +22645,8 @@
       <c r="H505">
         <v>2.1675</v>
       </c>
-      <c r="I505" t="s">
-        <v>14</v>
+      <c r="I505">
+        <v>0</v>
       </c>
       <c r="J505">
         <v>273</v>
@@ -22698,8 +22689,8 @@
       <c r="H506">
         <v>2.3889</v>
       </c>
-      <c r="I506" t="s">
-        <v>14</v>
+      <c r="I506">
+        <v>0</v>
       </c>
       <c r="J506">
         <v>273</v>
@@ -22742,8 +22733,8 @@
       <c r="H507">
         <v>2.5049999999999999</v>
       </c>
-      <c r="I507" t="s">
-        <v>14</v>
+      <c r="I507">
+        <v>0</v>
       </c>
       <c r="J507">
         <v>273</v>
@@ -22762,6 +22753,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N507" xr:uid="{68233791-F9D2-0643-935C-5A6412DEF1C5}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>